--- a/Mercy_Sangura_Thesis_Final/Mud_crab_analysis_workbook.xlsx
+++ b/Mercy_Sangura_Thesis_Final/Mud_crab_analysis_workbook.xlsx
@@ -20,11 +20,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Obj2 Payment Pricing" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Obj2 Relationships" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Price Analysis" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Obj3 Constraints" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Obj3 Regulation" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Site Associations" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charts" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clean Data" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market Structure" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Obj3 Constraints" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Obj3 Regulation" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Site Associations" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charts" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clean Data" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9999,6 +10000,902 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Market Structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Percentages are valid percentages within the actor category at that BMU. A dash means the actor was not sampled there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Table 41</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Concentration of First-Sale Outlets Reported by Fishers, by BMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>BMU</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Fishers answering</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Buying points named</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Largest point</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Share at the largest point</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>HHI</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Numbers equivalent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Shimoni</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Mkuyuni</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>64.0%</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>4,592</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Majoreni</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Majoreni / Aleni</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>92.3%</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>8,580</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Vanga</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Kiwegu</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>5,850</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Msambweni</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Gasi</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>5,556</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>All four BMUs</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Majoreni / Aleni</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>30.2%</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>2,371</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>4.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Table 42</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Buyer Options per Harvester and Harvesters per Trader, by BMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>BMU</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Fishers answering</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Selling to one buyer only</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Mean buyers per fisher</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Fishers sampled</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Middlemen sampled</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Fishers per middleman</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Shimoni</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>17 (68.0%)</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>2.27 : 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Majoreni</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>10 (71.4%)</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>2.00 : 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Vanga</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>18 (85.7%)</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>5.25 : 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Msambweni</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>3 (100.0%)</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>no trader sampled</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>All four BMUs</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>50 (76.9%)</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>2.95 : 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Table 43</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Gross Marketing Margin, Total Margin and Producer’s Share by Chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Fisher KSh/kg</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Middleman KSh/kg</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>Final node KSh/kg</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>Middleman GMM</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Final node GMM</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Total GMM</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>Producer’s share</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>Producer’s share net of loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Large (Grade A) sold on to exporters</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>604.6</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>945.5</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>1,700.0</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>36.1%</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>64.4%</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>35.6%</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>31.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Large (Grade A) sold on to hoteliers</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>604.6</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>945.5</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>2,200.0</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>36.1%</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>57.0%</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>72.5%</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>27.5%</t>
+        </is>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>24.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Medium (Grade B) sold on to exporters</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>514.6</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>718.2</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>1,300.0</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>28.3%</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>44.8%</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>60.4%</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>39.6%</t>
+        </is>
+      </c>
+      <c r="I32" s="11" t="inlineStr">
+        <is>
+          <t>35.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Table 44</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Price Dispersion Within Each Actor Category and Price Transmission to the Fisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Size grade</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Fisher</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Middleman</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Hotelier</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>Exporter</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>Shimoni</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>Majoreni</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>Vanga</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Coefficient of variation of reported price, by actor category</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Large (Grade A)</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>31.8%</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>14.9%</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>25.9%</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>6.8%</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr"/>
+      <c r="G40" s="9" t="inlineStr"/>
+      <c r="H40" s="9" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>Medium (Grade B)</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>31.8%</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>14.0%</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>28.8%</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>8.9%</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr"/>
+      <c r="G41" s="9" t="inlineStr"/>
+      <c r="H41" s="9" t="inlineStr"/>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Fisher price as a percentage of the middleman price at the same BMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>Large (Grade A)</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr"/>
+      <c r="C43" s="9" t="inlineStr"/>
+      <c r="D43" s="9" t="inlineStr"/>
+      <c r="E43" s="9" t="inlineStr"/>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>55.0%</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>91.7%</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>53.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>Medium (Grade B)</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr"/>
+      <c r="C44" s="11" t="inlineStr"/>
+      <c r="D44" s="11" t="inlineStr"/>
+      <c r="E44" s="11" t="inlineStr"/>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>54.2%</t>
+        </is>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>91.3%</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>76.8%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -10031,7 +10928,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Table 41</t>
+          <t>Table 45</t>
         </is>
       </c>
     </row>
@@ -10795,7 +11692,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Table 42</t>
+          <t>Table 46</t>
         </is>
       </c>
     </row>
@@ -11035,7 +11932,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Table 43</t>
+          <t>Table 47</t>
         </is>
       </c>
     </row>
@@ -11806,7 +12703,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>Table 44</t>
+          <t>Table 48</t>
         </is>
       </c>
     </row>
@@ -12218,7 +13115,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Table 45</t>
+          <t>Table 49</t>
         </is>
       </c>
     </row>
@@ -13162,7 +14059,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13200,7 +14097,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Table 46</t>
+          <t>Table 50</t>
         </is>
       </c>
     </row>
@@ -13974,7 +14871,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Table 47</t>
+          <t>Table 51</t>
         </is>
       </c>
     </row>
@@ -14738,7 +15635,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Table 48</t>
+          <t>Table 52</t>
         </is>
       </c>
     </row>
@@ -15332,7 +16229,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15370,7 +16267,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Table 49</t>
+          <t>Table 53</t>
         </is>
       </c>
     </row>
@@ -15820,7 +16717,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16400,7 +17297,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Mercy_Sangura_Thesis_Final/Mud_crab_analysis_workbook.xlsx
+++ b/Mercy_Sangura_Thesis_Final/Mud_crab_analysis_workbook.xlsx
@@ -2075,11 +2075,7 @@
           <t>3 kg</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 0</t>
-        </is>
-      </c>
+      <c r="B10" s="9" t="inlineStr"/>
       <c r="C10" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -2118,11 +2114,7 @@
           <t>5 kg</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 0</t>
-        </is>
-      </c>
+      <c r="B11" s="9" t="inlineStr"/>
       <c r="C11" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -2161,11 +2153,7 @@
           <t>Above 10 kg</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 0</t>
-        </is>
-      </c>
+      <c r="B12" s="9" t="inlineStr"/>
       <c r="C12" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -2251,11 +2239,7 @@
           <t>3 kg</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B14" s="9" t="inlineStr"/>
       <c r="C14" s="9" t="inlineStr">
         <is>
           <t>9 (40.9%)</t>
@@ -2294,11 +2278,7 @@
           <t>5 kg</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B15" s="9" t="inlineStr"/>
       <c r="C15" s="9" t="inlineStr">
         <is>
           <t>13 (59.1%)</t>
@@ -2337,11 +2317,7 @@
           <t>Above 10 kg</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B16" s="9" t="inlineStr"/>
       <c r="C16" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -2423,11 +2399,7 @@
           <t>3 kg</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B18" s="9" t="inlineStr"/>
       <c r="C18" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -2466,11 +2438,7 @@
           <t>5 kg</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B19" s="9" t="inlineStr"/>
       <c r="C19" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -2509,11 +2477,7 @@
           <t>Above 10 kg</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B20" s="9" t="inlineStr"/>
       <c r="C20" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -2595,11 +2559,7 @@
           <t>3 kg</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B22" s="9" t="inlineStr"/>
       <c r="C22" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -2638,11 +2598,7 @@
           <t>5 kg</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B23" s="9" t="inlineStr"/>
       <c r="C23" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -2681,11 +2637,7 @@
           <t>Above 10 kg</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B24" s="11" t="inlineStr"/>
       <c r="C24" s="11" t="inlineStr">
         <is>
           <t>4 (100.0%)</t>
@@ -3115,11 +3067,7 @@
           <t>Seasonal factors only</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B21" s="9" t="inlineStr"/>
       <c r="C21" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -3158,11 +3106,7 @@
           <t>Seasonal, weather and regulatory factors</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B22" s="9" t="inlineStr"/>
       <c r="C22" s="9" t="inlineStr">
         <is>
           <t>65 (100.0%)</t>
@@ -3248,11 +3192,7 @@
           <t>Seasonal factors only</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B24" s="9" t="inlineStr"/>
       <c r="C24" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -3291,11 +3231,7 @@
           <t>Seasonal, weather and regulatory factors</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B25" s="9" t="inlineStr"/>
       <c r="C25" s="9" t="inlineStr">
         <is>
           <t>8 (36.4%)</t>
@@ -3377,11 +3313,7 @@
           <t>Seasonal factors only</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B27" s="9" t="inlineStr"/>
       <c r="C27" s="9" t="inlineStr">
         <is>
           <t>5 (100.0%)</t>
@@ -3420,11 +3352,7 @@
           <t>Seasonal, weather and regulatory factors</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B28" s="9" t="inlineStr"/>
       <c r="C28" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -3506,11 +3434,7 @@
           <t>Seasonal factors only</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B30" s="9" t="inlineStr"/>
       <c r="C30" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -3549,11 +3473,7 @@
           <t>Seasonal, weather and regulatory factors</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B31" s="11" t="inlineStr"/>
       <c r="C31" s="11" t="inlineStr">
         <is>
           <t>4 (100.0%)</t>
@@ -3743,11 +3663,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 9</t>
-        </is>
-      </c>
+      <c r="B10" s="9" t="inlineStr"/>
       <c r="C10" s="9" t="inlineStr">
         <is>
           <t>9 (100.0%)</t>
@@ -3829,11 +3745,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B12" s="9" t="inlineStr"/>
       <c r="C12" s="9" t="inlineStr">
         <is>
           <t>1 (4.5%)</t>
@@ -3915,11 +3827,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B14" s="9" t="inlineStr"/>
       <c r="C14" s="9" t="inlineStr">
         <is>
           <t>5 (100.0%)</t>
@@ -4001,11 +3909,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B16" s="9" t="inlineStr"/>
       <c r="C16" s="9" t="inlineStr">
         <is>
           <t>4 (100.0%)</t>
@@ -4273,11 +4177,7 @@
           <t>Fixed price</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B24" s="9" t="inlineStr"/>
       <c r="C24" s="9" t="inlineStr">
         <is>
           <t>9 (13.8%)</t>
@@ -4316,11 +4216,7 @@
           <t>Frequency supply</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B25" s="9" t="inlineStr"/>
       <c r="C25" s="9" t="inlineStr">
         <is>
           <t>18 (27.7%)</t>
@@ -4402,11 +4298,7 @@
           <t>Fixed price</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 11</t>
-        </is>
-      </c>
+      <c r="B27" s="9" t="inlineStr"/>
       <c r="C27" s="9" t="inlineStr">
         <is>
           <t>1 (9.1%)</t>
@@ -4445,11 +4337,7 @@
           <t>Frequency supply</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 11</t>
-        </is>
-      </c>
+      <c r="B28" s="9" t="inlineStr"/>
       <c r="C28" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -4531,11 +4419,7 @@
           <t>Fixed price</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B30" s="9" t="inlineStr"/>
       <c r="C30" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -4574,11 +4458,7 @@
           <t>Frequency supply</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B31" s="9" t="inlineStr"/>
       <c r="C31" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -4660,11 +4540,7 @@
           <t>Fixed price</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B33" s="9" t="inlineStr"/>
       <c r="C33" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -4703,11 +4579,7 @@
           <t>Frequency supply</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B34" s="11" t="inlineStr"/>
       <c r="C34" s="11" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -4857,11 +4729,7 @@
           <t>Frequency supply</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 56</t>
-        </is>
-      </c>
+      <c r="B43" s="9" t="inlineStr"/>
       <c r="C43" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -4900,11 +4768,7 @@
           <t>Frequency supply and credit</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 56</t>
-        </is>
-      </c>
+      <c r="B44" s="9" t="inlineStr"/>
       <c r="C44" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -4943,11 +4807,7 @@
           <t>Supply quantity</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 56</t>
-        </is>
-      </c>
+      <c r="B45" s="9" t="inlineStr"/>
       <c r="C45" s="9" t="inlineStr">
         <is>
           <t>56 (100.0%)</t>
@@ -5029,11 +4889,7 @@
           <t>Frequency supply</t>
         </is>
       </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 21</t>
-        </is>
-      </c>
+      <c r="B47" s="9" t="inlineStr"/>
       <c r="C47" s="9" t="inlineStr">
         <is>
           <t>4 (19.0%)</t>
@@ -5072,11 +4928,7 @@
           <t>Frequency supply and credit</t>
         </is>
       </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 21</t>
-        </is>
-      </c>
+      <c r="B48" s="9" t="inlineStr"/>
       <c r="C48" s="9" t="inlineStr">
         <is>
           <t>2 (9.5%)</t>
@@ -5115,11 +4967,7 @@
           <t>Supply quantity</t>
         </is>
       </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 21</t>
-        </is>
-      </c>
+      <c r="B49" s="9" t="inlineStr"/>
       <c r="C49" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -5201,11 +5049,7 @@
           <t>Frequency supply</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 0</t>
-        </is>
-      </c>
+      <c r="B51" s="9" t="inlineStr"/>
       <c r="C51" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -5244,11 +5088,7 @@
           <t>Frequency supply and credit</t>
         </is>
       </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 0</t>
-        </is>
-      </c>
+      <c r="B52" s="9" t="inlineStr"/>
       <c r="C52" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -5287,11 +5127,7 @@
           <t>Supply quantity</t>
         </is>
       </c>
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 0</t>
-        </is>
-      </c>
+      <c r="B53" s="9" t="inlineStr"/>
       <c r="C53" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -5373,11 +5209,7 @@
           <t>Frequency supply</t>
         </is>
       </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 0</t>
-        </is>
-      </c>
+      <c r="B55" s="9" t="inlineStr"/>
       <c r="C55" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -5416,11 +5248,7 @@
           <t>Frequency supply and credit</t>
         </is>
       </c>
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 0</t>
-        </is>
-      </c>
+      <c r="B56" s="9" t="inlineStr"/>
       <c r="C56" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -5459,11 +5287,7 @@
           <t>Supply quantity</t>
         </is>
       </c>
-      <c r="B57" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 0</t>
-        </is>
-      </c>
+      <c r="B57" s="11" t="inlineStr"/>
       <c r="C57" s="11" t="inlineStr">
         <is>
           <t>-</t>
@@ -5613,11 +5437,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B66" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B66" s="9" t="inlineStr"/>
       <c r="C66" s="9" t="inlineStr">
         <is>
           <t>65 (100.0%)</t>
@@ -5699,11 +5519,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B68" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B68" s="9" t="inlineStr"/>
       <c r="C68" s="9" t="inlineStr">
         <is>
           <t>1 (4.5%)</t>
@@ -5785,11 +5601,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B70" s="9" t="inlineStr"/>
       <c r="C70" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -5871,11 +5683,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B72" s="9" t="inlineStr"/>
       <c r="C72" s="9" t="inlineStr">
         <is>
           <t>4 (100.0%)</t>
@@ -5964,11 +5772,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B75" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B75" s="9" t="inlineStr"/>
       <c r="C75" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -6050,11 +5854,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B77" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B77" s="9" t="inlineStr"/>
       <c r="C77" s="9" t="inlineStr">
         <is>
           <t>11 (50.0%)</t>
@@ -6136,11 +5936,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B79" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B79" s="9" t="inlineStr"/>
       <c r="C79" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -6222,11 +6018,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B81" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B81" s="9" t="inlineStr"/>
       <c r="C81" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -6315,11 +6107,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 10</t>
-        </is>
-      </c>
+      <c r="B84" s="9" t="inlineStr"/>
       <c r="C84" s="9" t="inlineStr">
         <is>
           <t>9 (90.0%)</t>
@@ -6401,11 +6189,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B86" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B86" s="9" t="inlineStr"/>
       <c r="C86" s="9" t="inlineStr">
         <is>
           <t>1 (4.5%)</t>
@@ -6487,11 +6271,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B88" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B88" s="9" t="inlineStr"/>
       <c r="C88" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -6573,11 +6353,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B90" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B90" s="11" t="inlineStr"/>
       <c r="C90" s="11" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -6731,11 +6507,7 @@
           <t>Negotiation</t>
         </is>
       </c>
-      <c r="B99" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B99" s="9" t="inlineStr"/>
       <c r="C99" s="9" t="inlineStr">
         <is>
           <t>41 (63.1%)</t>
@@ -6774,11 +6546,7 @@
           <t>Negotiation and marketing</t>
         </is>
       </c>
-      <c r="B100" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B100" s="9" t="inlineStr"/>
       <c r="C100" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -6864,11 +6632,7 @@
           <t>Negotiation</t>
         </is>
       </c>
-      <c r="B102" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B102" s="9" t="inlineStr"/>
       <c r="C102" s="9" t="inlineStr">
         <is>
           <t>7 (31.8%)</t>
@@ -6907,11 +6671,7 @@
           <t>Negotiation and marketing</t>
         </is>
       </c>
-      <c r="B103" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B103" s="9" t="inlineStr"/>
       <c r="C103" s="9" t="inlineStr">
         <is>
           <t>14 (63.6%)</t>
@@ -6993,11 +6753,7 @@
           <t>Negotiation</t>
         </is>
       </c>
-      <c r="B105" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B105" s="9" t="inlineStr"/>
       <c r="C105" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -7036,11 +6792,7 @@
           <t>Negotiation and marketing</t>
         </is>
       </c>
-      <c r="B106" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B106" s="9" t="inlineStr"/>
       <c r="C106" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -7122,11 +6874,7 @@
           <t>Negotiation</t>
         </is>
       </c>
-      <c r="B108" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B108" s="9" t="inlineStr"/>
       <c r="C108" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -7165,11 +6913,7 @@
           <t>Negotiation and marketing</t>
         </is>
       </c>
-      <c r="B109" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B109" s="9" t="inlineStr"/>
       <c r="C109" s="9" t="inlineStr">
         <is>
           <t>4 (100.0%)</t>
@@ -7258,11 +7002,7 @@
           <t>Flexible terms and competitive bidding</t>
         </is>
       </c>
-      <c r="B112" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B112" s="9" t="inlineStr"/>
       <c r="C112" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -7344,11 +7084,7 @@
           <t>Flexible terms and competitive bidding</t>
         </is>
       </c>
-      <c r="B114" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B114" s="9" t="inlineStr"/>
       <c r="C114" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -7430,11 +7166,7 @@
           <t>Flexible terms and competitive bidding</t>
         </is>
       </c>
-      <c r="B116" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B116" s="9" t="inlineStr"/>
       <c r="C116" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -7516,11 +7248,7 @@
           <t>Flexible terms and competitive bidding</t>
         </is>
       </c>
-      <c r="B118" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B118" s="11" t="inlineStr"/>
       <c r="C118" s="11" t="inlineStr">
         <is>
           <t>4 (100.0%)</t>
@@ -7983,7 +7711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -8854,498 +8582,538 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Marketing Margins and the Distribution of the Final Chain Price Across Actor Nodes</t>
+          <t>Mean Reported Mud Crab Price by Actor Category, BMU and Size Grade</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>Market node</t>
+          <t>BMU</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Mean price (KSh/kg)</t>
+          <t>Fisher M KSh/kg (n)</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Value retained or margin added (KSh/kg)</t>
+          <t>Middleman M KSh/kg (n)</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Margin as % of the fisher price</t>
+          <t>Hotelier M KSh/kg (n)</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>% of the final chain price</t>
+          <t>Exporter M KSh/kg (n)</t>
         </is>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>Large (Grade A) sold on to exporters</t>
+          <t>Large (Grade A)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>Fisher (first sale)</t>
+          <t>Shimoni</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>604.6</t>
+          <t>540.0 (25)</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>604.6</t>
+          <t>981.8 (11)</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1,500.0 (1)</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>Middleman</t>
+          <t>Majoreni</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>945.5</t>
+          <t>785.7 (14)</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>340.8</t>
+          <t>857.1 (7)</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>Exporter (end of chain)</t>
+          <t>Vanga</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>1,700.0</t>
+          <t>535.7 (21)</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>754.5</t>
+          <t>1,000.0 (4)</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>124.8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>Hotelier (not in this chain)</t>
+          <t>Msambweni</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>650.0 (3)</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="28" customHeight="1">
-      <c r="A53" s="12" t="inlineStr">
-        <is>
-          <t>Large (Grade A) sold on to hoteliers</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>Other sites</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>800.0 (2)</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>2,375.0 (4)</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>1,700.0 (4)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>Fisher (first sale)</t>
+          <t>All sites</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>604.6</t>
+          <t>604.6 (65)</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>604.6</t>
+          <t>945.5 (22)</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2,200.0 (5)</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>27.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>Middleman</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>945.5</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>340.8</t>
-        </is>
-      </c>
-      <c r="D55" s="9" t="inlineStr">
-        <is>
-          <t>56.4</t>
-        </is>
-      </c>
-      <c r="E55" s="9" t="inlineStr">
-        <is>
-          <t>15.5</t>
+          <t>1,700.0 (4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>Medium (Grade B)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>Hotelier (end of chain)</t>
+          <t>Shimoni</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>2,200.0</t>
+          <t>404.0 (25)</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>1,254.5</t>
+          <t>745.5 (11)</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>207.5</t>
+          <t>300.0 (1)</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>Exporter (not in this chain)</t>
+          <t>Majoreni</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>600.0 (14)</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>657.1 (7)</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="28" customHeight="1">
-      <c r="A58" s="12" t="inlineStr">
-        <is>
-          <t>Medium (Grade B) sold on to exporters</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>Vanga</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>576.2 (21)</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>750.0 (4)</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>Fisher (first sale)</t>
+          <t>Msambweni</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>514.6</t>
+          <t>616.7 (3)</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>514.6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>Middleman</t>
+          <t>Other sites</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>718.2</t>
+          <t>500.0 (2)</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>203.6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>400.0 (4)</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>1,300.0 (4)</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
-          <t>Exporter (end of chain)</t>
-        </is>
-      </c>
-      <c r="B61" s="9" t="inlineStr">
-        <is>
-          <t>1,300.0</t>
-        </is>
-      </c>
-      <c r="C61" s="9" t="inlineStr">
-        <is>
-          <t>581.8</t>
-        </is>
-      </c>
-      <c r="D61" s="9" t="inlineStr">
-        <is>
-          <t>113.1</t>
-        </is>
-      </c>
-      <c r="E61" s="9" t="inlineStr">
-        <is>
-          <t>44.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="10" t="inlineStr">
-        <is>
-          <t>Hotelier (not in this chain)</t>
-        </is>
-      </c>
-      <c r="B62" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C62" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D62" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E62" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>All sites</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>514.6 (65)</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>718.2 (22)</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>380.0 (5)</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>1,300.0 (4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Table 39</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>Table 39</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="5" t="inlineStr">
-        <is>
-          <t>Mean Reported Mud Crab Price by Actor Category, BMU and Size Grade</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>First-Sale Price Spread Between Fishers and Middlemen Within Each BMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>BMU</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>Fisher M KSh/kg (n)</t>
-        </is>
-      </c>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t>Middleman M KSh/kg (n)</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>Hotelier M KSh/kg (n)</t>
-        </is>
-      </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>Exporter M KSh/kg (n)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="28" customHeight="1">
-      <c r="A69" s="12" t="inlineStr">
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>Fisher M (KSh/kg)</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>Middleman M (KSh/kg)</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>Spread (KSh/kg)</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>Spread as % of the fisher price</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>Fisher price as % of the middleman price</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="28" customHeight="1">
+      <c r="A68" s="12" t="inlineStr">
         <is>
           <t>Large (Grade A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>Shimoni</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>540.0</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>981.8</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>441.8</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>55.0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>Shimoni</t>
+          <t>Majoreni</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>540.0 (25)</t>
+          <t>785.7</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>981.8 (11)</t>
+          <t>857.1</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>1,500.0 (1)</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>91.7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>Majoreni</t>
+          <t>Vanga</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>785.7 (14)</t>
+          <t>535.7</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>857.1 (7)</t>
+          <t>1,000.0</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>464.3</t>
         </is>
       </c>
       <c r="E71" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>86.7</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>53.6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>Vanga</t>
+          <t>Msambweni</t>
         </is>
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>535.7 (21)</t>
+          <t>650.0</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>1,000.0 (4)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
@@ -9354,6 +9122,11 @@
         </is>
       </c>
       <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9362,12 +9135,12 @@
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>Msambweni</t>
+          <t>Other sites</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>650.0 (3)</t>
+          <t>800.0</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
@@ -9385,607 +9158,412 @@
           <t>-</t>
         </is>
       </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="8" t="inlineStr">
-        <is>
-          <t>Other sites</t>
-        </is>
-      </c>
-      <c r="B74" s="9" t="inlineStr">
-        <is>
-          <t>800.0 (2)</t>
-        </is>
-      </c>
-      <c r="C74" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D74" s="9" t="inlineStr">
-        <is>
-          <t>2,375.0 (4)</t>
-        </is>
-      </c>
-      <c r="E74" s="9" t="inlineStr">
-        <is>
-          <t>1,700.0 (4)</t>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="28" customHeight="1">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t>Medium (Grade B)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>All sites</t>
+          <t>Shimoni</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>604.6 (65)</t>
+          <t>404.0</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>945.5 (22)</t>
+          <t>745.5</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>2,200.0 (5)</t>
+          <t>341.5</t>
         </is>
       </c>
       <c r="E75" s="9" t="inlineStr">
         <is>
-          <t>1,700.0 (4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="28" customHeight="1">
-      <c r="A76" s="12" t="inlineStr">
-        <is>
-          <t>Medium (Grade B)</t>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>Majoreni</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>600.0</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>657.1</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>57.1</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>91.3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>Shimoni</t>
+          <t>Vanga</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>404.0 (25)</t>
+          <t>576.2</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>745.5 (11)</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>300.0 (1)</t>
+          <t>173.8</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30.2</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>76.8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
+          <t>Msambweni</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>616.7</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>Other sites</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>Table 40</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>Concentration of First-Sale Outlets Reported by Fishers, by BMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>BMU</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>Fishers answering</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>Buying points named</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>Largest point</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>Share at the largest point</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>HHI</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>Numbers equivalent</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>Shimoni</t>
+        </is>
+      </c>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>Mkuyuni</t>
+        </is>
+      </c>
+      <c r="E86" s="9" t="inlineStr">
+        <is>
+          <t>64.0%</t>
+        </is>
+      </c>
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>4,592</t>
+        </is>
+      </c>
+      <c r="G86" s="9" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
           <t>Majoreni</t>
         </is>
       </c>
-      <c r="B78" s="9" t="inlineStr">
-        <is>
-          <t>600.0 (14)</t>
-        </is>
-      </c>
-      <c r="C78" s="9" t="inlineStr">
-        <is>
-          <t>657.1 (7)</t>
-        </is>
-      </c>
-      <c r="D78" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E78" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="8" t="inlineStr">
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>Majoreni / Aleni</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>92.3%</t>
+        </is>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>8,580</t>
+        </is>
+      </c>
+      <c r="G87" s="9" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="inlineStr">
         <is>
           <t>Vanga</t>
         </is>
       </c>
-      <c r="B79" s="9" t="inlineStr">
-        <is>
-          <t>576.2 (21)</t>
-        </is>
-      </c>
-      <c r="C79" s="9" t="inlineStr">
-        <is>
-          <t>750.0 (4)</t>
-        </is>
-      </c>
-      <c r="D79" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E79" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="8" t="inlineStr">
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>Kiwegu</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>5,850</t>
+        </is>
+      </c>
+      <c r="G88" s="9" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
         <is>
           <t>Msambweni</t>
         </is>
       </c>
-      <c r="B80" s="9" t="inlineStr">
-        <is>
-          <t>616.7 (3)</t>
-        </is>
-      </c>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D80" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E80" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="8" t="inlineStr">
-        <is>
-          <t>Other sites</t>
-        </is>
-      </c>
-      <c r="B81" s="9" t="inlineStr">
-        <is>
-          <t>500.0 (2)</t>
-        </is>
-      </c>
-      <c r="C81" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D81" s="9" t="inlineStr">
-        <is>
-          <t>400.0 (4)</t>
-        </is>
-      </c>
-      <c r="E81" s="9" t="inlineStr">
-        <is>
-          <t>1,300.0 (4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="10" t="inlineStr">
-        <is>
-          <t>All sites</t>
-        </is>
-      </c>
-      <c r="B82" s="11" t="inlineStr">
-        <is>
-          <t>514.6 (65)</t>
-        </is>
-      </c>
-      <c r="C82" s="11" t="inlineStr">
-        <is>
-          <t>718.2 (22)</t>
-        </is>
-      </c>
-      <c r="D82" s="11" t="inlineStr">
-        <is>
-          <t>380.0 (5)</t>
-        </is>
-      </c>
-      <c r="E82" s="11" t="inlineStr">
-        <is>
-          <t>1,300.0 (4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>Table 40</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>First-Sale Price Spread Between Fishers and Middlemen Within Each BMU</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="30" customHeight="1">
-      <c r="A88" s="6" t="inlineStr">
-        <is>
-          <t>BMU</t>
-        </is>
-      </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>Fisher M (KSh/kg)</t>
-        </is>
-      </c>
-      <c r="C88" s="7" t="inlineStr">
-        <is>
-          <t>Middleman M (KSh/kg)</t>
-        </is>
-      </c>
-      <c r="D88" s="7" t="inlineStr">
-        <is>
-          <t>Spread (KSh/kg)</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>Spread as % of the fisher price</t>
-        </is>
-      </c>
-      <c r="F88" s="7" t="inlineStr">
-        <is>
-          <t>Fisher price as % of the middleman price</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="28" customHeight="1">
-      <c r="A89" s="12" t="inlineStr">
-        <is>
-          <t>Large (Grade A)</t>
+      <c r="B89" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>Gasi</t>
+        </is>
+      </c>
+      <c r="E89" s="9" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="F89" s="9" t="inlineStr">
+        <is>
+          <t>5,556</t>
+        </is>
+      </c>
+      <c r="G89" s="9" t="inlineStr">
+        <is>
+          <t>1.80</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t>Shimoni</t>
-        </is>
-      </c>
-      <c r="B90" s="9" t="inlineStr">
-        <is>
-          <t>540.0</t>
-        </is>
-      </c>
-      <c r="C90" s="9" t="inlineStr">
-        <is>
-          <t>981.8</t>
-        </is>
-      </c>
-      <c r="D90" s="9" t="inlineStr">
-        <is>
-          <t>441.8</t>
-        </is>
-      </c>
-      <c r="E90" s="9" t="inlineStr">
-        <is>
-          <t>81.8</t>
-        </is>
-      </c>
-      <c r="F90" s="9" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="8" t="inlineStr">
-        <is>
-          <t>Majoreni</t>
-        </is>
-      </c>
-      <c r="B91" s="9" t="inlineStr">
-        <is>
-          <t>785.7</t>
-        </is>
-      </c>
-      <c r="C91" s="9" t="inlineStr">
-        <is>
-          <t>857.1</t>
-        </is>
-      </c>
-      <c r="D91" s="9" t="inlineStr">
-        <is>
-          <t>71.4</t>
-        </is>
-      </c>
-      <c r="E91" s="9" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="F91" s="9" t="inlineStr">
-        <is>
-          <t>91.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="8" t="inlineStr">
-        <is>
-          <t>Vanga</t>
-        </is>
-      </c>
-      <c r="B92" s="9" t="inlineStr">
-        <is>
-          <t>535.7</t>
-        </is>
-      </c>
-      <c r="C92" s="9" t="inlineStr">
-        <is>
-          <t>1,000.0</t>
-        </is>
-      </c>
-      <c r="D92" s="9" t="inlineStr">
-        <is>
-          <t>464.3</t>
-        </is>
-      </c>
-      <c r="E92" s="9" t="inlineStr">
-        <is>
-          <t>86.7</t>
-        </is>
-      </c>
-      <c r="F92" s="9" t="inlineStr">
-        <is>
-          <t>53.6</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="8" t="inlineStr">
-        <is>
-          <t>Msambweni</t>
-        </is>
-      </c>
-      <c r="B93" s="9" t="inlineStr">
-        <is>
-          <t>650.0</t>
-        </is>
-      </c>
-      <c r="C93" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D93" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E93" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F93" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="8" t="inlineStr">
-        <is>
-          <t>Other sites</t>
-        </is>
-      </c>
-      <c r="B94" s="9" t="inlineStr">
-        <is>
-          <t>800.0</t>
-        </is>
-      </c>
-      <c r="C94" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D94" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E94" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F94" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="28" customHeight="1">
-      <c r="A95" s="12" t="inlineStr">
-        <is>
-          <t>Medium (Grade B)</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="8" t="inlineStr">
-        <is>
-          <t>Shimoni</t>
-        </is>
-      </c>
-      <c r="B96" s="9" t="inlineStr">
-        <is>
-          <t>404.0</t>
-        </is>
-      </c>
-      <c r="C96" s="9" t="inlineStr">
-        <is>
-          <t>745.5</t>
-        </is>
-      </c>
-      <c r="D96" s="9" t="inlineStr">
-        <is>
-          <t>341.5</t>
-        </is>
-      </c>
-      <c r="E96" s="9" t="inlineStr">
-        <is>
-          <t>84.5</t>
-        </is>
-      </c>
-      <c r="F96" s="9" t="inlineStr">
-        <is>
-          <t>54.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="8" t="inlineStr">
-        <is>
-          <t>Majoreni</t>
-        </is>
-      </c>
-      <c r="B97" s="9" t="inlineStr">
-        <is>
-          <t>600.0</t>
-        </is>
-      </c>
-      <c r="C97" s="9" t="inlineStr">
-        <is>
-          <t>657.1</t>
-        </is>
-      </c>
-      <c r="D97" s="9" t="inlineStr">
-        <is>
-          <t>57.1</t>
-        </is>
-      </c>
-      <c r="E97" s="9" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="F97" s="9" t="inlineStr">
-        <is>
-          <t>91.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="8" t="inlineStr">
-        <is>
-          <t>Vanga</t>
-        </is>
-      </c>
-      <c r="B98" s="9" t="inlineStr">
-        <is>
-          <t>576.2</t>
-        </is>
-      </c>
-      <c r="C98" s="9" t="inlineStr">
-        <is>
-          <t>750.0</t>
-        </is>
-      </c>
-      <c r="D98" s="9" t="inlineStr">
-        <is>
-          <t>173.8</t>
-        </is>
-      </c>
-      <c r="E98" s="9" t="inlineStr">
-        <is>
-          <t>30.2</t>
-        </is>
-      </c>
-      <c r="F98" s="9" t="inlineStr">
-        <is>
-          <t>76.8</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="8" t="inlineStr">
-        <is>
-          <t>Msambweni</t>
-        </is>
-      </c>
-      <c r="B99" s="9" t="inlineStr">
-        <is>
-          <t>616.7</t>
-        </is>
-      </c>
-      <c r="C99" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E99" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F99" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="10" t="inlineStr">
-        <is>
-          <t>Other sites</t>
-        </is>
-      </c>
-      <c r="B100" s="11" t="inlineStr">
-        <is>
-          <t>500.0</t>
-        </is>
-      </c>
-      <c r="C100" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E100" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F100" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>All four BMUs</t>
+        </is>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="C90" s="11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D90" s="11" t="inlineStr">
+        <is>
+          <t>Majoreni / Aleni</t>
+        </is>
+      </c>
+      <c r="E90" s="11" t="inlineStr">
+        <is>
+          <t>30.2%</t>
+        </is>
+      </c>
+      <c r="F90" s="11" t="inlineStr">
+        <is>
+          <t>2,371</t>
+        </is>
+      </c>
+      <c r="G90" s="11" t="inlineStr">
+        <is>
+          <t>4.22</t>
         </is>
       </c>
     </row>
@@ -10000,7 +9578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -10039,7 +9617,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Concentration of First-Sale Outlets Reported by Fishers, by BMU</t>
+          <t>Buyer Options per Harvester and Harvesters per Trader, by BMU</t>
         </is>
       </c>
     </row>
@@ -10056,27 +9634,27 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Buying points named</t>
+          <t>Selling to one buyer only</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Largest point</t>
+          <t>Mean buyers per fisher</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Share at the largest point</t>
+          <t>Fishers sampled</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>HHI</t>
+          <t>Middlemen sampled</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Numbers equivalent</t>
+          <t>Fishers per middleman</t>
         </is>
       </c>
     </row>
@@ -10093,27 +9671,27 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>17 (68.0%)</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Mkuyuni</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>4,592</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.27 : 1</t>
         </is>
       </c>
     </row>
@@ -10125,32 +9703,32 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10 (71.4%)</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Majoreni / Aleni</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>8,580</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>2.00 : 1</t>
         </is>
       </c>
     </row>
@@ -10162,32 +9740,32 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
+          <t>18 (85.7%)</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>Kiwegu</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>5,850</t>
-        </is>
-      </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>5.25 : 1</t>
         </is>
       </c>
     </row>
@@ -10204,27 +9782,27 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3 (100.0%)</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Gasi</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>5,556</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>no trader sampled</t>
         </is>
       </c>
     </row>
@@ -10236,32 +9814,32 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>50 (76.9%)</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Majoreni / Aleni</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F12" s="11" t="inlineStr">
         <is>
-          <t>2,371</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>2.95 : 1</t>
         </is>
       </c>
     </row>
@@ -10275,611 +9853,761 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Buyer Options per Harvester and Harvesters per Trader, by BMU</t>
+          <t>Marketing Margins and the Distribution of the Final Chain Price Across Actor Nodes</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>BMU</t>
+          <t>Market node</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Fishers answering</t>
+          <t>Mean price (KSh/kg)</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Selling to one buyer only</t>
+          <t>Value retained or margin added (KSh/kg)</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Mean buyers per fisher</t>
+          <t>Margin as % of the fisher price</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Fishers sampled</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>Middlemen sampled</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>Fishers per middleman</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>Shimoni</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>17 (68.0%)</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>2.27 : 1</t>
+          <t>% of the final chain price</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Large (Grade A) sold on to exporters</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Majoreni</t>
+          <t>Fisher (first sale)</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>604.6</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>10 (71.4%)</t>
+          <t>604.6</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>2.00 : 1</t>
+          <t>35.6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Vanga</t>
+          <t>Middleman</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>945.5</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>18 (85.7%)</t>
+          <t>340.8</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>5.25 : 1</t>
+          <t>20.0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Msambweni</t>
+          <t>Exporter (end of chain)</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1,700.0</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>3 (100.0%)</t>
+          <t>754.5</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>124.8</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>no trader sampled</t>
+          <t>44.4</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>All four BMUs</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>50 (76.9%)</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="G23" s="11" t="inlineStr">
-        <is>
-          <t>2.95 : 1</t>
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Hotelier (not in this chain)</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Large (Grade A) sold on to hoteliers</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Fisher (first sale)</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>604.6</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>604.6</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>27.5</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Table 43</t>
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Middleman</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>945.5</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>340.8</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>15.5</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Gross Marketing Margin, Total Margin and Producer’s Share by Chain</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Chain</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Fisher KSh/kg</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>Middleman KSh/kg</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>Final node KSh/kg</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>Middleman GMM</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>Final node GMM</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>Total GMM</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>Producer’s share</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>Producer’s share net of loss</t>
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Hotelier (end of chain)</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>2,200.0</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>1,254.5</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>207.5</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>57.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Exporter (not in this chain)</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Medium (Grade B) sold on to exporters</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>Large (Grade A) sold on to exporters</t>
+          <t>Fisher (first sale)</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>604.6</t>
+          <t>514.6</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>945.5</t>
+          <t>514.6</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>1,700.0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
         <is>
-          <t>36.1%</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>64.4%</t>
-        </is>
-      </c>
-      <c r="H30" s="9" t="inlineStr">
-        <is>
-          <t>35.6%</t>
-        </is>
-      </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>31.9%</t>
+          <t>39.6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Large (Grade A) sold on to hoteliers</t>
+          <t>Middleman</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>604.6</t>
+          <t>718.2</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>945.5</t>
+          <t>203.6</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>2,200.0</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>36.1%</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>57.0%</t>
-        </is>
-      </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>72.5%</t>
-        </is>
-      </c>
-      <c r="H31" s="9" t="inlineStr">
-        <is>
-          <t>27.5%</t>
-        </is>
-      </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>24.6%</t>
+          <t>15.7</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>Medium (Grade B) sold on to exporters</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>514.6</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>718.2</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Exporter (end of chain)</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>1,300.0</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>28.3%</t>
-        </is>
-      </c>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>44.8%</t>
-        </is>
-      </c>
-      <c r="G32" s="11" t="inlineStr">
-        <is>
-          <t>60.4%</t>
-        </is>
-      </c>
-      <c r="H32" s="11" t="inlineStr">
-        <is>
-          <t>39.6%</t>
-        </is>
-      </c>
-      <c r="I32" s="11" t="inlineStr">
-        <is>
-          <t>35.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>Table 44</t>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>581.8</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>113.1</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Hotelier (not in this chain)</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Price Dispersion Within Each Actor Category and Price Transmission to the Fisher</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>Size grade</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Fisher</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>Middleman</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>Hotelier</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>Exporter</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>Shimoni</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>Majoreni</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="inlineStr">
-        <is>
-          <t>Vanga</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t>Coefficient of variation of reported price, by actor category</t>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Table 43</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Gross Marketing Margin, Total Margin and Producer’s Share by Chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Fisher KSh/kg</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Middleman KSh/kg</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>Final node KSh/kg</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Middleman GMM</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>Final node GMM</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>Total GMM</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>Producer’s share</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>Producer’s share net of loss</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Large (Grade A)</t>
+          <t>Large (Grade A) sold on to exporters</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>604.6</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>945.5</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>1,700.0</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>6.8%</t>
-        </is>
-      </c>
-      <c r="F40" s="9" t="inlineStr"/>
-      <c r="G40" s="9" t="inlineStr"/>
-      <c r="H40" s="9" t="inlineStr"/>
+          <t>36.1%</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>64.4%</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>35.6%</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>31.9%</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
+          <t>Large (Grade A) sold on to hoteliers</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>604.6</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>945.5</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>2,200.0</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>36.1%</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>57.0%</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>72.5%</t>
+        </is>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>27.5%</t>
+        </is>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>24.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>Medium (Grade B) sold on to exporters</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>514.6</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>718.2</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>1,300.0</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>28.3%</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>44.8%</t>
+        </is>
+      </c>
+      <c r="G42" s="11" t="inlineStr">
+        <is>
+          <t>60.4%</t>
+        </is>
+      </c>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>39.6%</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="inlineStr">
+        <is>
+          <t>35.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Table 44</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Price Dispersion Within Each Actor Category and Price Transmission to the Fisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Size grade</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Fisher</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Middleman</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Hotelier</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>Exporter</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>Shimoni</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>Majoreni</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>Vanga</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>Coefficient of variation of reported price, by actor category</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>Large (Grade A)</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>31.8%</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>14.9%</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>25.9%</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>6.8%</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr"/>
+      <c r="G50" s="9" t="inlineStr"/>
+      <c r="H50" s="9" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
           <t>Medium (Grade B)</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>31.8%</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>14.0%</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D51" s="9" t="inlineStr">
         <is>
           <t>28.8%</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="E51" s="9" t="inlineStr">
         <is>
           <t>8.9%</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr"/>
-      <c r="G41" s="9" t="inlineStr"/>
-      <c r="H41" s="9" t="inlineStr"/>
-    </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="12" t="inlineStr">
+      <c r="F51" s="9" t="inlineStr"/>
+      <c r="G51" s="9" t="inlineStr"/>
+      <c r="H51" s="9" t="inlineStr"/>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="12" t="inlineStr">
         <is>
           <t>Fisher price as a percentage of the middleman price at the same BMU</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>Large (Grade A)</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr"/>
-      <c r="C43" s="9" t="inlineStr"/>
-      <c r="D43" s="9" t="inlineStr"/>
-      <c r="E43" s="9" t="inlineStr"/>
-      <c r="F43" s="9" t="inlineStr">
+      <c r="B53" s="9" t="inlineStr"/>
+      <c r="C53" s="9" t="inlineStr"/>
+      <c r="D53" s="9" t="inlineStr"/>
+      <c r="E53" s="9" t="inlineStr"/>
+      <c r="F53" s="9" t="inlineStr">
         <is>
           <t>55.0%</t>
         </is>
       </c>
-      <c r="G43" s="9" t="inlineStr">
+      <c r="G53" s="9" t="inlineStr">
         <is>
           <t>91.7%</t>
         </is>
       </c>
-      <c r="H43" s="9" t="inlineStr">
+      <c r="H53" s="9" t="inlineStr">
         <is>
           <t>53.6%</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>Medium (Grade B)</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr"/>
-      <c r="C44" s="11" t="inlineStr"/>
-      <c r="D44" s="11" t="inlineStr"/>
-      <c r="E44" s="11" t="inlineStr"/>
-      <c r="F44" s="11" t="inlineStr">
+      <c r="B54" s="11" t="inlineStr"/>
+      <c r="C54" s="11" t="inlineStr"/>
+      <c r="D54" s="11" t="inlineStr"/>
+      <c r="E54" s="11" t="inlineStr"/>
+      <c r="F54" s="11" t="inlineStr">
         <is>
           <t>54.2%</t>
         </is>
       </c>
-      <c r="G44" s="11" t="inlineStr">
+      <c r="G54" s="11" t="inlineStr">
         <is>
           <t>91.3%</t>
         </is>
       </c>
-      <c r="H44" s="11" t="inlineStr">
+      <c r="H54" s="11" t="inlineStr">
         <is>
           <t>76.8%</t>
         </is>
@@ -11046,11 +10774,7 @@
           <t>Mortality</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B10" s="9" t="inlineStr"/>
       <c r="C10" s="9" t="inlineStr">
         <is>
           <t>6 (9.2%)</t>
@@ -11089,11 +10813,7 @@
           <t>Market seasonality</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B11" s="9" t="inlineStr"/>
       <c r="C11" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -11132,11 +10852,7 @@
           <t>High freight, flight delays and supply risk</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B12" s="9" t="inlineStr"/>
       <c r="C12" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -11222,11 +10938,7 @@
           <t>Mortality</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B14" s="9" t="inlineStr"/>
       <c r="C14" s="9" t="inlineStr">
         <is>
           <t>11 (50.0%)</t>
@@ -11265,11 +10977,7 @@
           <t>Market seasonality</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B15" s="9" t="inlineStr"/>
       <c r="C15" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -11308,11 +11016,7 @@
           <t>High freight, flight delays and supply risk</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B16" s="9" t="inlineStr"/>
       <c r="C16" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -11394,11 +11098,7 @@
           <t>Mortality</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B18" s="9" t="inlineStr"/>
       <c r="C18" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -11437,11 +11137,7 @@
           <t>Market seasonality</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B19" s="9" t="inlineStr"/>
       <c r="C19" s="9" t="inlineStr">
         <is>
           <t>5 (100.0%)</t>
@@ -11480,11 +11176,7 @@
           <t>High freight, flight delays and supply risk</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B20" s="9" t="inlineStr"/>
       <c r="C20" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -11566,11 +11258,7 @@
           <t>Mortality</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B22" s="9" t="inlineStr"/>
       <c r="C22" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -11609,11 +11297,7 @@
           <t>Market seasonality</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B23" s="9" t="inlineStr"/>
       <c r="C23" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -11652,11 +11336,7 @@
           <t>High freight, flight delays and supply risk</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B24" s="11" t="inlineStr"/>
       <c r="C24" s="11" t="inlineStr">
         <is>
           <t>4 (100.0%)</t>
@@ -12050,11 +11730,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B44" s="9" t="inlineStr"/>
       <c r="C44" s="9" t="inlineStr">
         <is>
           <t>4 (6.2%)</t>
@@ -12136,11 +11812,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B46" s="9" t="inlineStr"/>
       <c r="C46" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -12222,11 +11894,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B48" s="9" t="inlineStr"/>
       <c r="C48" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -12308,11 +11976,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B50" s="9" t="inlineStr"/>
       <c r="C50" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -12405,11 +12069,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B53" s="9" t="inlineStr"/>
       <c r="C53" s="9" t="inlineStr">
         <is>
           <t>12 (18.5%)</t>
@@ -12491,11 +12151,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B55" s="9" t="inlineStr"/>
       <c r="C55" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -12577,11 +12233,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B57" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B57" s="9" t="inlineStr"/>
       <c r="C57" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -12663,11 +12315,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B59" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B59" s="11" t="inlineStr"/>
       <c r="C59" s="11" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -12817,11 +12465,7 @@
           <t>Insurance and diversification</t>
         </is>
       </c>
-      <c r="B68" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B68" s="9" t="inlineStr"/>
       <c r="C68" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -12903,11 +12547,7 @@
           <t>Insurance and diversification</t>
         </is>
       </c>
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B70" s="9" t="inlineStr"/>
       <c r="C70" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -12989,11 +12629,7 @@
           <t>Insurance and diversification</t>
         </is>
       </c>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B72" s="9" t="inlineStr"/>
       <c r="C72" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -13075,11 +12711,7 @@
           <t>Insurance and diversification</t>
         </is>
       </c>
-      <c r="B74" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B74" s="11" t="inlineStr"/>
       <c r="C74" s="11" t="inlineStr">
         <is>
           <t>4 (100.0%)</t>
@@ -13408,11 +13040,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B88" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B88" s="9" t="inlineStr"/>
       <c r="C88" s="9" t="inlineStr">
         <is>
           <t>65 (100.0%)</t>
@@ -13494,11 +13122,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B90" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B90" s="9" t="inlineStr"/>
       <c r="C90" s="9" t="inlineStr">
         <is>
           <t>22 (100.0%)</t>
@@ -13580,11 +13204,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B92" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B92" s="9" t="inlineStr"/>
       <c r="C92" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -13666,11 +13286,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B94" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B94" s="9" t="inlineStr"/>
       <c r="C94" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -13759,11 +13375,7 @@
           <t>Flexibility and collaboration</t>
         </is>
       </c>
-      <c r="B97" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B97" s="9" t="inlineStr"/>
       <c r="C97" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -13845,11 +13457,7 @@
           <t>Flexibility and collaboration</t>
         </is>
       </c>
-      <c r="B99" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B99" s="9" t="inlineStr"/>
       <c r="C99" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -13931,11 +13539,7 @@
           <t>Flexibility and collaboration</t>
         </is>
       </c>
-      <c r="B101" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B101" s="9" t="inlineStr"/>
       <c r="C101" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -14017,11 +13621,7 @@
           <t>Flexibility and collaboration</t>
         </is>
       </c>
-      <c r="B103" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B103" s="11" t="inlineStr"/>
       <c r="C103" s="11" t="inlineStr">
         <is>
           <t>4 (100.0%)</t>
@@ -14211,11 +13811,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B10" s="9" t="inlineStr"/>
       <c r="C10" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -14301,11 +13897,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B12" s="9" t="inlineStr"/>
       <c r="C12" s="9" t="inlineStr">
         <is>
           <t>6 (27.3%)</t>
@@ -14387,11 +13979,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B14" s="9" t="inlineStr"/>
       <c r="C14" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -14473,11 +14061,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B16" s="9" t="inlineStr"/>
       <c r="C16" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -14989,11 +14573,7 @@
           <t>Disagree</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B35" s="9" t="inlineStr"/>
       <c r="C35" s="9" t="inlineStr">
         <is>
           <t>52 (80.0%)</t>
@@ -15032,11 +14612,7 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B36" s="9" t="inlineStr"/>
       <c r="C36" s="9" t="inlineStr">
         <is>
           <t>11 (16.9%)</t>
@@ -15075,11 +14651,7 @@
           <t>Agree</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B37" s="9" t="inlineStr"/>
       <c r="C37" s="9" t="inlineStr">
         <is>
           <t>2 (3.1%)</t>
@@ -15165,11 +14737,7 @@
           <t>Disagree</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B39" s="9" t="inlineStr"/>
       <c r="C39" s="9" t="inlineStr">
         <is>
           <t>8 (36.4%)</t>
@@ -15208,11 +14776,7 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B40" s="9" t="inlineStr"/>
       <c r="C40" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -15251,11 +14815,7 @@
           <t>Agree</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B41" s="9" t="inlineStr"/>
       <c r="C41" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -15337,11 +14897,7 @@
           <t>Disagree</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B43" s="9" t="inlineStr"/>
       <c r="C43" s="9" t="inlineStr">
         <is>
           <t>5 (100.0%)</t>
@@ -15380,11 +14936,7 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B44" s="9" t="inlineStr"/>
       <c r="C44" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -15423,11 +14975,7 @@
           <t>Agree</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B45" s="9" t="inlineStr"/>
       <c r="C45" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -15509,11 +15057,7 @@
           <t>Disagree</t>
         </is>
       </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B47" s="9" t="inlineStr"/>
       <c r="C47" s="9" t="inlineStr">
         <is>
           <t>4 (100.0%)</t>
@@ -15552,11 +15096,7 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B48" s="9" t="inlineStr"/>
       <c r="C48" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -15595,11 +15135,7 @@
           <t>Agree</t>
         </is>
       </c>
-      <c r="B49" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B49" s="11" t="inlineStr"/>
       <c r="C49" s="11" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -15753,11 +15289,7 @@
           <t>Disagree</t>
         </is>
       </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B58" s="9" t="inlineStr"/>
       <c r="C58" s="9" t="inlineStr">
         <is>
           <t>11 (16.9%)</t>
@@ -15796,11 +15328,7 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="B59" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B59" s="9" t="inlineStr"/>
       <c r="C59" s="9" t="inlineStr">
         <is>
           <t>48 (73.8%)</t>
@@ -15886,11 +15414,7 @@
           <t>Disagree</t>
         </is>
       </c>
-      <c r="B61" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B61" s="9" t="inlineStr"/>
       <c r="C61" s="9" t="inlineStr">
         <is>
           <t>7 (31.8%)</t>
@@ -15929,11 +15453,7 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="B62" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B62" s="9" t="inlineStr"/>
       <c r="C62" s="9" t="inlineStr">
         <is>
           <t>1 (4.5%)</t>
@@ -16015,11 +15535,7 @@
           <t>Disagree</t>
         </is>
       </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B64" s="9" t="inlineStr"/>
       <c r="C64" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -16058,11 +15574,7 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="B65" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B65" s="9" t="inlineStr"/>
       <c r="C65" s="9" t="inlineStr">
         <is>
           <t>5 (100.0%)</t>
@@ -16144,11 +15656,7 @@
           <t>Disagree</t>
         </is>
       </c>
-      <c r="B67" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B67" s="9" t="inlineStr"/>
       <c r="C67" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -16187,11 +15695,7 @@
           <t>Neutral</t>
         </is>
       </c>
-      <c r="B68" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B68" s="11" t="inlineStr"/>
       <c r="C68" s="11" t="inlineStr">
         <is>
           <t>4 (100.0%)</t>
@@ -60828,11 +60332,7 @@
           <t>18-35</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B10" s="9" t="inlineStr"/>
       <c r="C10" s="9" t="inlineStr">
         <is>
           <t>35 (53.8%)</t>
@@ -60871,11 +60371,7 @@
           <t>36-49</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B11" s="9" t="inlineStr"/>
       <c r="C11" s="9" t="inlineStr">
         <is>
           <t>12 (18.5%)</t>
@@ -60914,11 +60410,7 @@
           <t>50-60</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B12" s="9" t="inlineStr"/>
       <c r="C12" s="9" t="inlineStr">
         <is>
           <t>10 (15.4%)</t>
@@ -60957,11 +60449,7 @@
           <t>Over 60</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B13" s="9" t="inlineStr"/>
       <c r="C13" s="9" t="inlineStr">
         <is>
           <t>4 (6.2%)</t>
@@ -61047,11 +60535,7 @@
           <t>18-35</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B15" s="9" t="inlineStr"/>
       <c r="C15" s="9" t="inlineStr">
         <is>
           <t>5 (22.7%)</t>
@@ -61090,11 +60574,7 @@
           <t>36-49</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B16" s="9" t="inlineStr"/>
       <c r="C16" s="9" t="inlineStr">
         <is>
           <t>11 (50.0%)</t>
@@ -61133,11 +60613,7 @@
           <t>50-60</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B17" s="9" t="inlineStr"/>
       <c r="C17" s="9" t="inlineStr">
         <is>
           <t>5 (22.7%)</t>
@@ -61176,11 +60652,7 @@
           <t>Over 60</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B18" s="9" t="inlineStr"/>
       <c r="C18" s="9" t="inlineStr">
         <is>
           <t>1 (4.5%)</t>
@@ -61262,11 +60734,7 @@
           <t>18-35</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B20" s="9" t="inlineStr"/>
       <c r="C20" s="9" t="inlineStr">
         <is>
           <t>4 (80.0%)</t>
@@ -61305,11 +60773,7 @@
           <t>36-49</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B21" s="9" t="inlineStr"/>
       <c r="C21" s="9" t="inlineStr">
         <is>
           <t>1 (20.0%)</t>
@@ -61348,11 +60812,7 @@
           <t>50-60</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B22" s="9" t="inlineStr"/>
       <c r="C22" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -61391,11 +60851,7 @@
           <t>Over 60</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B23" s="9" t="inlineStr"/>
       <c r="C23" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -61477,11 +60933,7 @@
           <t>18-35</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B25" s="9" t="inlineStr"/>
       <c r="C25" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -61520,11 +60972,7 @@
           <t>36-49</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B26" s="9" t="inlineStr"/>
       <c r="C26" s="9" t="inlineStr">
         <is>
           <t>4 (100.0%)</t>
@@ -61563,11 +61011,7 @@
           <t>50-60</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B27" s="9" t="inlineStr"/>
       <c r="C27" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -61606,11 +61050,7 @@
           <t>Over 60</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B28" s="11" t="inlineStr"/>
       <c r="C28" s="11" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -61760,11 +61200,7 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B37" s="9" t="inlineStr"/>
       <c r="C37" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -61846,11 +61282,7 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B39" s="9" t="inlineStr"/>
       <c r="C39" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -61932,11 +61364,7 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B41" s="9" t="inlineStr"/>
       <c r="C41" s="9" t="inlineStr">
         <is>
           <t>1 (20.0%)</t>
@@ -62018,11 +61446,7 @@
           <t>Female</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B43" s="11" t="inlineStr"/>
       <c r="C43" s="11" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -62176,11 +61600,7 @@
           <t>Duruma</t>
         </is>
       </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B52" s="9" t="inlineStr"/>
       <c r="C52" s="9" t="inlineStr">
         <is>
           <t>17 (26.2%)</t>
@@ -62219,11 +61639,7 @@
           <t>Vumba</t>
         </is>
       </c>
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B53" s="9" t="inlineStr"/>
       <c r="C53" s="9" t="inlineStr">
         <is>
           <t>12 (18.5%)</t>
@@ -62262,11 +61678,7 @@
           <t>Swahili</t>
         </is>
       </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B54" s="9" t="inlineStr"/>
       <c r="C54" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -62305,11 +61717,7 @@
           <t>Kikuyu</t>
         </is>
       </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B55" s="9" t="inlineStr"/>
       <c r="C55" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -62348,11 +61756,7 @@
           <t>Chinese</t>
         </is>
       </c>
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B56" s="9" t="inlineStr"/>
       <c r="C56" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -62438,11 +61842,7 @@
           <t>Duruma</t>
         </is>
       </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B58" s="9" t="inlineStr"/>
       <c r="C58" s="9" t="inlineStr">
         <is>
           <t>6 (27.3%)</t>
@@ -62481,11 +61881,7 @@
           <t>Vumba</t>
         </is>
       </c>
-      <c r="B59" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B59" s="9" t="inlineStr"/>
       <c r="C59" s="9" t="inlineStr">
         <is>
           <t>1 (4.5%)</t>
@@ -62524,11 +61920,7 @@
           <t>Swahili</t>
         </is>
       </c>
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B60" s="9" t="inlineStr"/>
       <c r="C60" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -62567,11 +61959,7 @@
           <t>Kikuyu</t>
         </is>
       </c>
-      <c r="B61" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B61" s="9" t="inlineStr"/>
       <c r="C61" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -62610,11 +61998,7 @@
           <t>Chinese</t>
         </is>
       </c>
-      <c r="B62" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B62" s="9" t="inlineStr"/>
       <c r="C62" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -62696,11 +62080,7 @@
           <t>Duruma</t>
         </is>
       </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B64" s="9" t="inlineStr"/>
       <c r="C64" s="9" t="inlineStr">
         <is>
           <t>1 (20.0%)</t>
@@ -62739,11 +62119,7 @@
           <t>Vumba</t>
         </is>
       </c>
-      <c r="B65" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B65" s="9" t="inlineStr"/>
       <c r="C65" s="9" t="inlineStr">
         <is>
           <t>2 (40.0%)</t>
@@ -62782,11 +62158,7 @@
           <t>Swahili</t>
         </is>
       </c>
-      <c r="B66" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B66" s="9" t="inlineStr"/>
       <c r="C66" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -62825,11 +62197,7 @@
           <t>Kikuyu</t>
         </is>
       </c>
-      <c r="B67" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B67" s="9" t="inlineStr"/>
       <c r="C67" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -62868,11 +62236,7 @@
           <t>Chinese</t>
         </is>
       </c>
-      <c r="B68" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B68" s="9" t="inlineStr"/>
       <c r="C68" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -62954,11 +62318,7 @@
           <t>Duruma</t>
         </is>
       </c>
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B70" s="9" t="inlineStr"/>
       <c r="C70" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -62997,11 +62357,7 @@
           <t>Vumba</t>
         </is>
       </c>
-      <c r="B71" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B71" s="9" t="inlineStr"/>
       <c r="C71" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -63040,11 +62396,7 @@
           <t>Swahili</t>
         </is>
       </c>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B72" s="9" t="inlineStr"/>
       <c r="C72" s="9" t="inlineStr">
         <is>
           <t>1 (25.0%)</t>
@@ -63083,11 +62435,7 @@
           <t>Kikuyu</t>
         </is>
       </c>
-      <c r="B73" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B73" s="9" t="inlineStr"/>
       <c r="C73" s="9" t="inlineStr">
         <is>
           <t>1 (25.0%)</t>
@@ -63126,11 +62474,7 @@
           <t>Chinese</t>
         </is>
       </c>
-      <c r="B74" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B74" s="11" t="inlineStr"/>
       <c r="C74" s="11" t="inlineStr">
         <is>
           <t>2 (50.0%)</t>
@@ -63284,11 +62628,7 @@
           <t>Married</t>
         </is>
       </c>
-      <c r="B83" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B83" s="9" t="inlineStr"/>
       <c r="C83" s="9" t="inlineStr">
         <is>
           <t>41 (63.1%)</t>
@@ -63327,11 +62667,7 @@
           <t>Separated / divorced</t>
         </is>
       </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B84" s="9" t="inlineStr"/>
       <c r="C84" s="9" t="inlineStr">
         <is>
           <t>3 (4.6%)</t>
@@ -63370,11 +62706,7 @@
           <t>Widowed</t>
         </is>
       </c>
-      <c r="B85" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B85" s="9" t="inlineStr"/>
       <c r="C85" s="9" t="inlineStr">
         <is>
           <t>1 (1.5%)</t>
@@ -63460,11 +62792,7 @@
           <t>Married</t>
         </is>
       </c>
-      <c r="B87" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B87" s="9" t="inlineStr"/>
       <c r="C87" s="9" t="inlineStr">
         <is>
           <t>20 (90.9%)</t>
@@ -63503,11 +62831,7 @@
           <t>Separated / divorced</t>
         </is>
       </c>
-      <c r="B88" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B88" s="9" t="inlineStr"/>
       <c r="C88" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -63546,11 +62870,7 @@
           <t>Widowed</t>
         </is>
       </c>
-      <c r="B89" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B89" s="9" t="inlineStr"/>
       <c r="C89" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -63632,11 +62952,7 @@
           <t>Married</t>
         </is>
       </c>
-      <c r="B91" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B91" s="9" t="inlineStr"/>
       <c r="C91" s="9" t="inlineStr">
         <is>
           <t>3 (60.0%)</t>
@@ -63675,11 +62991,7 @@
           <t>Separated / divorced</t>
         </is>
       </c>
-      <c r="B92" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B92" s="9" t="inlineStr"/>
       <c r="C92" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -63718,11 +63030,7 @@
           <t>Widowed</t>
         </is>
       </c>
-      <c r="B93" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B93" s="9" t="inlineStr"/>
       <c r="C93" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -63804,11 +63112,7 @@
           <t>Married</t>
         </is>
       </c>
-      <c r="B95" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B95" s="9" t="inlineStr"/>
       <c r="C95" s="9" t="inlineStr">
         <is>
           <t>4 (100.0%)</t>
@@ -63847,11 +63151,7 @@
           <t>Separated / divorced</t>
         </is>
       </c>
-      <c r="B96" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B96" s="9" t="inlineStr"/>
       <c r="C96" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -63890,11 +63190,7 @@
           <t>Widowed</t>
         </is>
       </c>
-      <c r="B97" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B97" s="11" t="inlineStr"/>
       <c r="C97" s="11" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -64048,11 +63344,7 @@
           <t>5-10 years</t>
         </is>
       </c>
-      <c r="B106" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B106" s="9" t="inlineStr"/>
       <c r="C106" s="9" t="inlineStr">
         <is>
           <t>22 (33.8%)</t>
@@ -64091,11 +63383,7 @@
           <t>11-20 years</t>
         </is>
       </c>
-      <c r="B107" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B107" s="9" t="inlineStr"/>
       <c r="C107" s="9" t="inlineStr">
         <is>
           <t>22 (33.8%)</t>
@@ -64134,11 +63422,7 @@
           <t>Over 20 years</t>
         </is>
       </c>
-      <c r="B108" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B108" s="9" t="inlineStr"/>
       <c r="C108" s="9" t="inlineStr">
         <is>
           <t>20 (30.8%)</t>
@@ -64224,11 +63508,7 @@
           <t>5-10 years</t>
         </is>
       </c>
-      <c r="B110" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B110" s="9" t="inlineStr"/>
       <c r="C110" s="9" t="inlineStr">
         <is>
           <t>3 (13.6%)</t>
@@ -64267,11 +63547,7 @@
           <t>11-20 years</t>
         </is>
       </c>
-      <c r="B111" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B111" s="9" t="inlineStr"/>
       <c r="C111" s="9" t="inlineStr">
         <is>
           <t>3 (13.6%)</t>
@@ -64310,11 +63586,7 @@
           <t>Over 20 years</t>
         </is>
       </c>
-      <c r="B112" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B112" s="9" t="inlineStr"/>
       <c r="C112" s="9" t="inlineStr">
         <is>
           <t>16 (72.7%)</t>
@@ -64396,11 +63668,7 @@
           <t>5-10 years</t>
         </is>
       </c>
-      <c r="B114" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B114" s="9" t="inlineStr"/>
       <c r="C114" s="9" t="inlineStr">
         <is>
           <t>1 (20.0%)</t>
@@ -64439,11 +63707,7 @@
           <t>11-20 years</t>
         </is>
       </c>
-      <c r="B115" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B115" s="9" t="inlineStr"/>
       <c r="C115" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -64482,11 +63746,7 @@
           <t>Over 20 years</t>
         </is>
       </c>
-      <c r="B116" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B116" s="9" t="inlineStr"/>
       <c r="C116" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -64568,11 +63828,7 @@
           <t>5-10 years</t>
         </is>
       </c>
-      <c r="B118" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B118" s="9" t="inlineStr"/>
       <c r="C118" s="9" t="inlineStr">
         <is>
           <t>2 (50.0%)</t>
@@ -64611,11 +63867,7 @@
           <t>11-20 years</t>
         </is>
       </c>
-      <c r="B119" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B119" s="9" t="inlineStr"/>
       <c r="C119" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -64654,11 +63906,7 @@
           <t>Over 20 years</t>
         </is>
       </c>
-      <c r="B120" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B120" s="11" t="inlineStr"/>
       <c r="C120" s="11" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -64848,11 +64096,7 @@
           <t>Exporter</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B10" s="9" t="inlineStr"/>
       <c r="C10" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -64891,11 +64135,7 @@
           <t>Marketer</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B11" s="9" t="inlineStr"/>
       <c r="C11" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -64934,11 +64174,7 @@
           <t>Processor</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B12" s="9" t="inlineStr"/>
       <c r="C12" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -65020,11 +64256,7 @@
           <t>Exporter</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B14" s="9" t="inlineStr"/>
       <c r="C14" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -65063,11 +64295,7 @@
           <t>Marketer</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B15" s="9" t="inlineStr"/>
       <c r="C15" s="9" t="inlineStr">
         <is>
           <t>22 (100.0%)</t>
@@ -65106,11 +64334,7 @@
           <t>Processor</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B16" s="9" t="inlineStr"/>
       <c r="C16" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -65192,11 +64416,7 @@
           <t>Exporter</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B18" s="9" t="inlineStr"/>
       <c r="C18" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -65235,11 +64455,7 @@
           <t>Marketer</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B19" s="9" t="inlineStr"/>
       <c r="C19" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -65278,11 +64494,7 @@
           <t>Processor</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B20" s="9" t="inlineStr"/>
       <c r="C20" s="9" t="inlineStr">
         <is>
           <t>5 (100.0%)</t>
@@ -65364,11 +64576,7 @@
           <t>Exporter</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B22" s="9" t="inlineStr"/>
       <c r="C22" s="9" t="inlineStr">
         <is>
           <t>4 (100.0%)</t>
@@ -65407,11 +64615,7 @@
           <t>Marketer</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B23" s="9" t="inlineStr"/>
       <c r="C23" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -65450,11 +64654,7 @@
           <t>Processor</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B24" s="9" t="inlineStr"/>
       <c r="C24" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -65787,11 +64987,7 @@
           <t>Medium-scale</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B38" s="9" t="inlineStr"/>
       <c r="C38" s="9" t="inlineStr">
         <is>
           <t>1 (1.5%)</t>
@@ -65830,11 +65026,7 @@
           <t>Large-scale</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B39" s="9" t="inlineStr"/>
       <c r="C39" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -65920,11 +65112,7 @@
           <t>Medium-scale</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B41" s="9" t="inlineStr"/>
       <c r="C41" s="9" t="inlineStr">
         <is>
           <t>10 (45.5%)</t>
@@ -65963,11 +65151,7 @@
           <t>Large-scale</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B42" s="9" t="inlineStr"/>
       <c r="C42" s="9" t="inlineStr">
         <is>
           <t>2 (9.1%)</t>
@@ -66049,11 +65233,7 @@
           <t>Medium-scale</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B44" s="9" t="inlineStr"/>
       <c r="C44" s="9" t="inlineStr">
         <is>
           <t>5 (100.0%)</t>
@@ -66092,11 +65272,7 @@
           <t>Large-scale</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B45" s="9" t="inlineStr"/>
       <c r="C45" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -66178,11 +65354,7 @@
           <t>Medium-scale</t>
         </is>
       </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B47" s="9" t="inlineStr"/>
       <c r="C47" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -66221,11 +65393,7 @@
           <t>Large-scale</t>
         </is>
       </c>
-      <c r="B48" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B48" s="11" t="inlineStr"/>
       <c r="C48" s="11" t="inlineStr">
         <is>
           <t>4 (100.0%)</t>
@@ -66814,11 +65982,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B75" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B75" s="9" t="inlineStr"/>
       <c r="C75" s="9" t="inlineStr">
         <is>
           <t>52 (80.0%)</t>
@@ -66900,11 +66064,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B77" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B77" s="9" t="inlineStr"/>
       <c r="C77" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -66986,11 +66146,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B79" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B79" s="9" t="inlineStr"/>
       <c r="C79" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -67072,11 +66228,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B81" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B81" s="9" t="inlineStr"/>
       <c r="C81" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -67169,11 +66321,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 64</t>
-        </is>
-      </c>
+      <c r="B84" s="9" t="inlineStr"/>
       <c r="C84" s="9" t="inlineStr">
         <is>
           <t>56 (87.5%)</t>
@@ -67259,11 +66407,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B86" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B86" s="9" t="inlineStr"/>
       <c r="C86" s="9" t="inlineStr">
         <is>
           <t>16 (72.7%)</t>
@@ -67345,11 +66489,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B88" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B88" s="9" t="inlineStr"/>
       <c r="C88" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -67431,11 +66571,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B90" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B90" s="9" t="inlineStr"/>
       <c r="C90" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -67524,11 +66660,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B93" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B93" s="9" t="inlineStr"/>
       <c r="C93" s="9" t="inlineStr">
         <is>
           <t>65 (100.0%)</t>
@@ -67614,11 +66746,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B95" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B95" s="9" t="inlineStr"/>
       <c r="C95" s="9" t="inlineStr">
         <is>
           <t>6 (27.3%)</t>
@@ -67700,11 +66828,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B97" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B97" s="9" t="inlineStr"/>
       <c r="C97" s="9" t="inlineStr">
         <is>
           <t>5 (100.0%)</t>
@@ -67786,11 +66910,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B99" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B99" s="11" t="inlineStr"/>
       <c r="C99" s="11" t="inlineStr">
         <is>
           <t>2 (50.0%)</t>
@@ -67944,11 +67064,7 @@
           <t>Formal institutions</t>
         </is>
       </c>
-      <c r="B108" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B108" s="9" t="inlineStr"/>
       <c r="C108" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -67987,11 +67103,7 @@
           <t>Middlemen</t>
         </is>
       </c>
-      <c r="B109" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B109" s="9" t="inlineStr"/>
       <c r="C109" s="9" t="inlineStr">
         <is>
           <t>61 (93.8%)</t>
@@ -68030,11 +67142,7 @@
           <t>Middlemen and relatives</t>
         </is>
       </c>
-      <c r="B110" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B110" s="9" t="inlineStr"/>
       <c r="C110" s="9" t="inlineStr">
         <is>
           <t>4 (6.2%)</t>
@@ -68120,11 +67228,7 @@
           <t>Formal institutions</t>
         </is>
       </c>
-      <c r="B112" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B112" s="9" t="inlineStr"/>
       <c r="C112" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -68163,11 +67267,7 @@
           <t>Middlemen</t>
         </is>
       </c>
-      <c r="B113" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B113" s="9" t="inlineStr"/>
       <c r="C113" s="9" t="inlineStr">
         <is>
           <t>10 (45.5%)</t>
@@ -68206,11 +67306,7 @@
           <t>Middlemen and relatives</t>
         </is>
       </c>
-      <c r="B114" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B114" s="9" t="inlineStr"/>
       <c r="C114" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -68292,11 +67388,7 @@
           <t>Formal institutions</t>
         </is>
       </c>
-      <c r="B116" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 0</t>
-        </is>
-      </c>
+      <c r="B116" s="9" t="inlineStr"/>
       <c r="C116" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -68335,11 +67427,7 @@
           <t>Middlemen</t>
         </is>
       </c>
-      <c r="B117" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 0</t>
-        </is>
-      </c>
+      <c r="B117" s="9" t="inlineStr"/>
       <c r="C117" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -68378,11 +67466,7 @@
           <t>Middlemen and relatives</t>
         </is>
       </c>
-      <c r="B118" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 0</t>
-        </is>
-      </c>
+      <c r="B118" s="9" t="inlineStr"/>
       <c r="C118" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -68464,11 +67548,7 @@
           <t>Formal institutions</t>
         </is>
       </c>
-      <c r="B120" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B120" s="9" t="inlineStr"/>
       <c r="C120" s="9" t="inlineStr">
         <is>
           <t>4 (100.0%)</t>
@@ -68507,11 +67587,7 @@
           <t>Middlemen</t>
         </is>
       </c>
-      <c r="B121" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B121" s="9" t="inlineStr"/>
       <c r="C121" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -68550,11 +67626,7 @@
           <t>Middlemen and relatives</t>
         </is>
       </c>
-      <c r="B122" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B122" s="11" t="inlineStr"/>
       <c r="C122" s="11" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -68748,11 +67820,7 @@
           <t>Other source</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 64</t>
-        </is>
-      </c>
+      <c r="B10" s="9" t="inlineStr"/>
       <c r="C10" s="9" t="inlineStr">
         <is>
           <t>23 (35.9%)</t>
@@ -68834,11 +67902,7 @@
           <t>Other source</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 0</t>
-        </is>
-      </c>
+      <c r="B12" s="9" t="inlineStr"/>
       <c r="C12" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -68920,11 +67984,7 @@
           <t>Other source</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 0</t>
-        </is>
-      </c>
+      <c r="B14" s="9" t="inlineStr"/>
       <c r="C14" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -69006,11 +68066,7 @@
           <t>Other source</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 0</t>
-        </is>
-      </c>
+      <c r="B16" s="9" t="inlineStr"/>
       <c r="C16" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -69103,11 +68159,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B19" s="9" t="inlineStr"/>
       <c r="C19" s="9" t="inlineStr">
         <is>
           <t>60 (92.3%)</t>
@@ -69189,11 +68241,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 0</t>
-        </is>
-      </c>
+      <c r="B21" s="9" t="inlineStr"/>
       <c r="C21" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -69275,11 +68323,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 0</t>
-        </is>
-      </c>
+      <c r="B23" s="9" t="inlineStr"/>
       <c r="C23" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -69361,11 +68405,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 0</t>
-        </is>
-      </c>
+      <c r="B25" s="11" t="inlineStr"/>
       <c r="C25" s="11" t="inlineStr">
         <is>
           <t>-</t>
@@ -69873,11 +68913,7 @@
           <t>Export markets</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B44" s="9" t="inlineStr"/>
       <c r="C44" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -69959,11 +68995,7 @@
           <t>Export markets</t>
         </is>
       </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B46" s="9" t="inlineStr"/>
       <c r="C46" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -70045,11 +69077,7 @@
           <t>Export markets</t>
         </is>
       </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B48" s="9" t="inlineStr"/>
       <c r="C48" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -70131,11 +69159,7 @@
           <t>Export markets</t>
         </is>
       </c>
-      <c r="B50" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B50" s="11" t="inlineStr"/>
       <c r="C50" s="11" t="inlineStr">
         <is>
           <t>4 (100.0%)</t>
@@ -70325,11 +69349,7 @@
           <t>Purchasing</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B10" s="9" t="inlineStr"/>
       <c r="C10" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -70411,11 +69431,7 @@
           <t>Purchasing</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B12" s="9" t="inlineStr"/>
       <c r="C12" s="9" t="inlineStr">
         <is>
           <t>22 (100.0%)</t>
@@ -70497,11 +69513,7 @@
           <t>Purchasing</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B14" s="9" t="inlineStr"/>
       <c r="C14" s="9" t="inlineStr">
         <is>
           <t>5 (100.0%)</t>
@@ -70583,11 +69595,7 @@
           <t>Purchasing</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B16" s="11" t="inlineStr"/>
       <c r="C16" s="11" t="inlineStr">
         <is>
           <t>4 (100.0%)</t>
@@ -70741,11 +69749,7 @@
           <t>Three-quarters</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B25" s="9" t="inlineStr"/>
       <c r="C25" s="9" t="inlineStr">
         <is>
           <t>13 (20.0%)</t>
@@ -70827,11 +69831,7 @@
           <t>Three-quarters</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 0</t>
-        </is>
-      </c>
+      <c r="B27" s="9" t="inlineStr"/>
       <c r="C27" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -70913,11 +69913,7 @@
           <t>Three-quarters</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 0</t>
-        </is>
-      </c>
+      <c r="B29" s="9" t="inlineStr"/>
       <c r="C29" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -70999,11 +69995,7 @@
           <t>Three-quarters</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 0</t>
-        </is>
-      </c>
+      <c r="B31" s="9" t="inlineStr"/>
       <c r="C31" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -71096,11 +70088,7 @@
           <t>6 hours</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B34" s="9" t="inlineStr"/>
       <c r="C34" s="9" t="inlineStr">
         <is>
           <t>43 (66.2%)</t>
@@ -71182,11 +70170,7 @@
           <t>6 hours</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 0</t>
-        </is>
-      </c>
+      <c r="B36" s="9" t="inlineStr"/>
       <c r="C36" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -71268,11 +70252,7 @@
           <t>6 hours</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 0</t>
-        </is>
-      </c>
+      <c r="B38" s="9" t="inlineStr"/>
       <c r="C38" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -71354,11 +70334,7 @@
           <t>6 hours</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 0</t>
-        </is>
-      </c>
+      <c r="B40" s="11" t="inlineStr"/>
       <c r="C40" s="11" t="inlineStr">
         <is>
           <t>-</t>
@@ -71548,11 +70524,7 @@
           <t>Local markets</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B10" s="9" t="inlineStr"/>
       <c r="C10" s="9" t="inlineStr">
         <is>
           <t>65 (100.0%)</t>
@@ -71591,11 +70563,7 @@
           <t>Restaurants and hotels</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B11" s="9" t="inlineStr"/>
       <c r="C11" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -71677,11 +70645,7 @@
           <t>Local markets</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B13" s="9" t="inlineStr"/>
       <c r="C13" s="9" t="inlineStr">
         <is>
           <t>22 (100.0%)</t>
@@ -71720,11 +70684,7 @@
           <t>Restaurants and hotels</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B14" s="9" t="inlineStr"/>
       <c r="C14" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -71806,11 +70766,7 @@
           <t>Local markets</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B16" s="9" t="inlineStr"/>
       <c r="C16" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -71849,11 +70805,7 @@
           <t>Restaurants and hotels</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B17" s="9" t="inlineStr"/>
       <c r="C17" s="9" t="inlineStr">
         <is>
           <t>5 (100.0%)</t>
@@ -71935,11 +70887,7 @@
           <t>Local markets</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B19" s="9" t="inlineStr"/>
       <c r="C19" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -71978,11 +70926,7 @@
           <t>Restaurants and hotels</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B20" s="9" t="inlineStr"/>
       <c r="C20" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -72071,11 +71015,7 @@
           <t>Direct contact</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B23" s="9" t="inlineStr"/>
       <c r="C23" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -72157,11 +71097,7 @@
           <t>Direct contact</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B25" s="9" t="inlineStr"/>
       <c r="C25" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -72243,11 +71179,7 @@
           <t>Direct contact</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B27" s="9" t="inlineStr"/>
       <c r="C27" s="9" t="inlineStr">
         <is>
           <t>5 (100.0%)</t>
@@ -72329,11 +71261,7 @@
           <t>Direct contact</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B29" s="11" t="inlineStr"/>
       <c r="C29" s="11" t="inlineStr">
         <is>
           <t>4 (100.0%)</t>
@@ -72487,11 +71415,7 @@
           <t>Two buyers</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B38" s="9" t="inlineStr"/>
       <c r="C38" s="9" t="inlineStr">
         <is>
           <t>15 (23.1%)</t>
@@ -72573,11 +71497,7 @@
           <t>Two buyers</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 0</t>
-        </is>
-      </c>
+      <c r="B40" s="9" t="inlineStr"/>
       <c r="C40" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -72659,11 +71579,7 @@
           <t>Two buyers</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 0</t>
-        </is>
-      </c>
+      <c r="B42" s="9" t="inlineStr"/>
       <c r="C42" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -72745,11 +71661,7 @@
           <t>Two buyers</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 0</t>
-        </is>
-      </c>
+      <c r="B44" s="9" t="inlineStr"/>
       <c r="C44" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -73257,11 +72169,7 @@
           <t>Market</t>
         </is>
       </c>
-      <c r="B63" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B63" s="9" t="inlineStr"/>
       <c r="C63" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -73300,11 +72208,7 @@
           <t>Town</t>
         </is>
       </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B64" s="9" t="inlineStr"/>
       <c r="C64" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -73390,11 +72294,7 @@
           <t>Market</t>
         </is>
       </c>
-      <c r="B66" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B66" s="9" t="inlineStr"/>
       <c r="C66" s="9" t="inlineStr">
         <is>
           <t>10 (45.5%)</t>
@@ -73433,11 +72333,7 @@
           <t>Town</t>
         </is>
       </c>
-      <c r="B67" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B67" s="9" t="inlineStr"/>
       <c r="C67" s="9" t="inlineStr">
         <is>
           <t>11 (50.0%)</t>
@@ -73519,11 +72415,7 @@
           <t>Market</t>
         </is>
       </c>
-      <c r="B69" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B69" s="9" t="inlineStr"/>
       <c r="C69" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -73562,11 +72454,7 @@
           <t>Town</t>
         </is>
       </c>
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B70" s="9" t="inlineStr"/>
       <c r="C70" s="9" t="inlineStr">
         <is>
           <t>5 (100.0%)</t>
@@ -73648,11 +72536,7 @@
           <t>Market</t>
         </is>
       </c>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B72" s="9" t="inlineStr"/>
       <c r="C72" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -73691,11 +72575,7 @@
           <t>Town</t>
         </is>
       </c>
-      <c r="B73" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B73" s="9" t="inlineStr"/>
       <c r="C73" s="9" t="inlineStr">
         <is>
           <t>4 (100.0%)</t>
@@ -74028,11 +72908,7 @@
           <t>Gasi</t>
         </is>
       </c>
-      <c r="B87" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 63</t>
-        </is>
-      </c>
+      <c r="B87" s="9" t="inlineStr"/>
       <c r="C87" s="9" t="inlineStr">
         <is>
           <t>2 (3.2%)</t>
@@ -74071,11 +72947,7 @@
           <t>Kiwegu</t>
         </is>
       </c>
-      <c r="B88" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 63</t>
-        </is>
-      </c>
+      <c r="B88" s="9" t="inlineStr"/>
       <c r="C88" s="9" t="inlineStr">
         <is>
           <t>16 (25.4%)</t>
@@ -74114,11 +72986,7 @@
           <t>Majoreni / Aleni</t>
         </is>
       </c>
-      <c r="B89" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 63</t>
-        </is>
-      </c>
+      <c r="B89" s="9" t="inlineStr"/>
       <c r="C89" s="9" t="inlineStr">
         <is>
           <t>19 (30.2%)</t>
@@ -74157,11 +73025,7 @@
           <t>Mkuyuni</t>
         </is>
       </c>
-      <c r="B90" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 63</t>
-        </is>
-      </c>
+      <c r="B90" s="9" t="inlineStr"/>
       <c r="C90" s="9" t="inlineStr">
         <is>
           <t>17 (27.0%)</t>
@@ -74200,11 +73064,7 @@
           <t>Mwambao</t>
         </is>
       </c>
-      <c r="B91" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 63</t>
-        </is>
-      </c>
+      <c r="B91" s="9" t="inlineStr"/>
       <c r="C91" s="9" t="inlineStr">
         <is>
           <t>1 (1.6%)</t>
@@ -74243,11 +73103,7 @@
           <t>Shimoni</t>
         </is>
       </c>
-      <c r="B92" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 63</t>
-        </is>
-      </c>
+      <c r="B92" s="9" t="inlineStr"/>
       <c r="C92" s="9" t="inlineStr">
         <is>
           <t>5 (7.9%)</t>
@@ -74286,11 +73142,7 @@
           <t>Vanga</t>
         </is>
       </c>
-      <c r="B93" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 63</t>
-        </is>
-      </c>
+      <c r="B93" s="9" t="inlineStr"/>
       <c r="C93" s="9" t="inlineStr">
         <is>
           <t>2 (3.2%)</t>
@@ -74372,11 +73224,7 @@
           <t>Gasi</t>
         </is>
       </c>
-      <c r="B95" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 0</t>
-        </is>
-      </c>
+      <c r="B95" s="9" t="inlineStr"/>
       <c r="C95" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -74415,11 +73263,7 @@
           <t>Kiwegu</t>
         </is>
       </c>
-      <c r="B96" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 0</t>
-        </is>
-      </c>
+      <c r="B96" s="9" t="inlineStr"/>
       <c r="C96" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -74458,11 +73302,7 @@
           <t>Majoreni / Aleni</t>
         </is>
       </c>
-      <c r="B97" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 0</t>
-        </is>
-      </c>
+      <c r="B97" s="9" t="inlineStr"/>
       <c r="C97" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -74501,11 +73341,7 @@
           <t>Mkuyuni</t>
         </is>
       </c>
-      <c r="B98" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 0</t>
-        </is>
-      </c>
+      <c r="B98" s="9" t="inlineStr"/>
       <c r="C98" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -74544,11 +73380,7 @@
           <t>Mwambao</t>
         </is>
       </c>
-      <c r="B99" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 0</t>
-        </is>
-      </c>
+      <c r="B99" s="9" t="inlineStr"/>
       <c r="C99" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -74587,11 +73419,7 @@
           <t>Shimoni</t>
         </is>
       </c>
-      <c r="B100" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 0</t>
-        </is>
-      </c>
+      <c r="B100" s="9" t="inlineStr"/>
       <c r="C100" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -74630,11 +73458,7 @@
           <t>Vanga</t>
         </is>
       </c>
-      <c r="B101" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 0</t>
-        </is>
-      </c>
+      <c r="B101" s="9" t="inlineStr"/>
       <c r="C101" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -74716,11 +73540,7 @@
           <t>Gasi</t>
         </is>
       </c>
-      <c r="B103" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 0</t>
-        </is>
-      </c>
+      <c r="B103" s="9" t="inlineStr"/>
       <c r="C103" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -74759,11 +73579,7 @@
           <t>Kiwegu</t>
         </is>
       </c>
-      <c r="B104" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 0</t>
-        </is>
-      </c>
+      <c r="B104" s="9" t="inlineStr"/>
       <c r="C104" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -74802,11 +73618,7 @@
           <t>Majoreni / Aleni</t>
         </is>
       </c>
-      <c r="B105" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 0</t>
-        </is>
-      </c>
+      <c r="B105" s="9" t="inlineStr"/>
       <c r="C105" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -74845,11 +73657,7 @@
           <t>Mkuyuni</t>
         </is>
       </c>
-      <c r="B106" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 0</t>
-        </is>
-      </c>
+      <c r="B106" s="9" t="inlineStr"/>
       <c r="C106" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -74888,11 +73696,7 @@
           <t>Mwambao</t>
         </is>
       </c>
-      <c r="B107" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 0</t>
-        </is>
-      </c>
+      <c r="B107" s="9" t="inlineStr"/>
       <c r="C107" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -74931,11 +73735,7 @@
           <t>Shimoni</t>
         </is>
       </c>
-      <c r="B108" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 0</t>
-        </is>
-      </c>
+      <c r="B108" s="9" t="inlineStr"/>
       <c r="C108" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -74974,11 +73774,7 @@
           <t>Vanga</t>
         </is>
       </c>
-      <c r="B109" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 0</t>
-        </is>
-      </c>
+      <c r="B109" s="9" t="inlineStr"/>
       <c r="C109" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -75060,11 +73856,7 @@
           <t>Gasi</t>
         </is>
       </c>
-      <c r="B111" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 0</t>
-        </is>
-      </c>
+      <c r="B111" s="9" t="inlineStr"/>
       <c r="C111" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -75103,11 +73895,7 @@
           <t>Kiwegu</t>
         </is>
       </c>
-      <c r="B112" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 0</t>
-        </is>
-      </c>
+      <c r="B112" s="9" t="inlineStr"/>
       <c r="C112" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -75146,11 +73934,7 @@
           <t>Majoreni / Aleni</t>
         </is>
       </c>
-      <c r="B113" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 0</t>
-        </is>
-      </c>
+      <c r="B113" s="9" t="inlineStr"/>
       <c r="C113" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -75189,11 +73973,7 @@
           <t>Mkuyuni</t>
         </is>
       </c>
-      <c r="B114" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 0</t>
-        </is>
-      </c>
+      <c r="B114" s="9" t="inlineStr"/>
       <c r="C114" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -75232,11 +74012,7 @@
           <t>Mwambao</t>
         </is>
       </c>
-      <c r="B115" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 0</t>
-        </is>
-      </c>
+      <c r="B115" s="9" t="inlineStr"/>
       <c r="C115" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -75275,11 +74051,7 @@
           <t>Shimoni</t>
         </is>
       </c>
-      <c r="B116" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 0</t>
-        </is>
-      </c>
+      <c r="B116" s="9" t="inlineStr"/>
       <c r="C116" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -75318,11 +74090,7 @@
           <t>Vanga</t>
         </is>
       </c>
-      <c r="B117" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 0</t>
-        </is>
-      </c>
+      <c r="B117" s="11" t="inlineStr"/>
       <c r="C117" s="11" t="inlineStr">
         <is>
           <t>-</t>
@@ -75472,11 +74240,7 @@
           <t>Majoreni / Aleni</t>
         </is>
       </c>
-      <c r="B126" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 15</t>
-        </is>
-      </c>
+      <c r="B126" s="9" t="inlineStr"/>
       <c r="C126" s="9" t="inlineStr">
         <is>
           <t>4 (26.7%)</t>
@@ -75515,11 +74279,7 @@
           <t>Mkuyuni</t>
         </is>
       </c>
-      <c r="B127" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 15</t>
-        </is>
-      </c>
+      <c r="B127" s="9" t="inlineStr"/>
       <c r="C127" s="9" t="inlineStr">
         <is>
           <t>8 (53.3%)</t>
@@ -75601,11 +74361,7 @@
           <t>Majoreni / Aleni</t>
         </is>
       </c>
-      <c r="B129" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 0</t>
-        </is>
-      </c>
+      <c r="B129" s="9" t="inlineStr"/>
       <c r="C129" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -75644,11 +74400,7 @@
           <t>Mkuyuni</t>
         </is>
       </c>
-      <c r="B130" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 0</t>
-        </is>
-      </c>
+      <c r="B130" s="9" t="inlineStr"/>
       <c r="C130" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -75730,11 +74482,7 @@
           <t>Majoreni / Aleni</t>
         </is>
       </c>
-      <c r="B132" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 0</t>
-        </is>
-      </c>
+      <c r="B132" s="9" t="inlineStr"/>
       <c r="C132" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -75773,11 +74521,7 @@
           <t>Mkuyuni</t>
         </is>
       </c>
-      <c r="B133" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 0</t>
-        </is>
-      </c>
+      <c r="B133" s="9" t="inlineStr"/>
       <c r="C133" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -75859,11 +74603,7 @@
           <t>Majoreni / Aleni</t>
         </is>
       </c>
-      <c r="B135" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 0</t>
-        </is>
-      </c>
+      <c r="B135" s="9" t="inlineStr"/>
       <c r="C135" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -75902,11 +74642,7 @@
           <t>Mkuyuni</t>
         </is>
       </c>
-      <c r="B136" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 0</t>
-        </is>
-      </c>
+      <c r="B136" s="11" t="inlineStr"/>
       <c r="C136" s="11" t="inlineStr">
         <is>
           <t>-</t>
@@ -76096,11 +74832,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B10" s="9" t="inlineStr"/>
       <c r="C10" s="9" t="inlineStr">
         <is>
           <t>65 (100.0%)</t>
@@ -76182,11 +74914,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B12" s="9" t="inlineStr"/>
       <c r="C12" s="9" t="inlineStr">
         <is>
           <t>22 (100.0%)</t>
@@ -76268,11 +74996,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B14" s="9" t="inlineStr"/>
       <c r="C14" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -76354,11 +75078,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B16" s="11" t="inlineStr"/>
       <c r="C16" s="11" t="inlineStr">
         <is>
           <t>4 (100.0%)</t>
@@ -76788,11 +75508,7 @@
           <t>Packaging standards</t>
         </is>
       </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B21" s="9" t="inlineStr"/>
       <c r="C21" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -76831,11 +75547,7 @@
           <t>Tying the claws</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B22" s="9" t="inlineStr"/>
       <c r="C22" s="9" t="inlineStr">
         <is>
           <t>65 (100.0%)</t>
@@ -76917,11 +75629,7 @@
           <t>Packaging standards</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B24" s="9" t="inlineStr"/>
       <c r="C24" s="9" t="inlineStr">
         <is>
           <t>21 (95.5%)</t>
@@ -76960,11 +75668,7 @@
           <t>Tying the claws</t>
         </is>
       </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B25" s="9" t="inlineStr"/>
       <c r="C25" s="9" t="inlineStr">
         <is>
           <t>1 (4.5%)</t>
@@ -77046,11 +75750,7 @@
           <t>Packaging standards</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B27" s="9" t="inlineStr"/>
       <c r="C27" s="9" t="inlineStr">
         <is>
           <t>5 (100.0%)</t>
@@ -77089,11 +75789,7 @@
           <t>Tying the claws</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B28" s="9" t="inlineStr"/>
       <c r="C28" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -77175,11 +75871,7 @@
           <t>Packaging standards</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B30" s="9" t="inlineStr"/>
       <c r="C30" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -77218,11 +75910,7 @@
           <t>Tying the claws</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B31" s="9" t="inlineStr"/>
       <c r="C31" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -77311,11 +75999,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B34" s="9" t="inlineStr"/>
       <c r="C34" s="9" t="inlineStr">
         <is>
           <t>65 (100.0%)</t>
@@ -77397,11 +76081,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B36" s="9" t="inlineStr"/>
       <c r="C36" s="9" t="inlineStr">
         <is>
           <t>22 (100.0%)</t>
@@ -77483,11 +76163,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B38" s="9" t="inlineStr"/>
       <c r="C38" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -77569,11 +76245,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B40" s="11" t="inlineStr"/>
       <c r="C40" s="11" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -77727,11 +76399,7 @@
           <t>All sizes / mixed</t>
         </is>
       </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B49" s="9" t="inlineStr"/>
       <c r="C49" s="9" t="inlineStr">
         <is>
           <t>12 (18.5%)</t>
@@ -77813,11 +76481,7 @@
           <t>All sizes / mixed</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 21</t>
-        </is>
-      </c>
+      <c r="B51" s="9" t="inlineStr"/>
       <c r="C51" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -77899,11 +76563,7 @@
           <t>All sizes / mixed</t>
         </is>
       </c>
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B53" s="9" t="inlineStr"/>
       <c r="C53" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -77985,11 +76645,7 @@
           <t>All sizes / mixed</t>
         </is>
       </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B55" s="9" t="inlineStr"/>
       <c r="C55" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -78078,11 +76734,7 @@
           <t>Mixed grade</t>
         </is>
       </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B58" s="9" t="inlineStr"/>
       <c r="C58" s="9" t="inlineStr">
         <is>
           <t>15 (23.1%)</t>
@@ -78164,11 +76816,7 @@
           <t>Mixed grade</t>
         </is>
       </c>
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B60" s="9" t="inlineStr"/>
       <c r="C60" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -78250,11 +76898,7 @@
           <t>Mixed grade</t>
         </is>
       </c>
-      <c r="B62" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 5</t>
-        </is>
-      </c>
+      <c r="B62" s="9" t="inlineStr"/>
       <c r="C62" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -78336,11 +76980,7 @@
           <t>Mixed grade</t>
         </is>
       </c>
-      <c r="B64" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B64" s="11" t="inlineStr"/>
       <c r="C64" s="11" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -78494,11 +77134,7 @@
           <t>Mixed size</t>
         </is>
       </c>
-      <c r="B73" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B73" s="9" t="inlineStr"/>
       <c r="C73" s="9" t="inlineStr">
         <is>
           <t>2 (3.1%)</t>
@@ -78580,11 +77216,7 @@
           <t>Mixed size</t>
         </is>
       </c>
-      <c r="B75" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B75" s="9" t="inlineStr"/>
       <c r="C75" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -78666,11 +77298,7 @@
           <t>Mixed size</t>
         </is>
       </c>
-      <c r="B77" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 0</t>
-        </is>
-      </c>
+      <c r="B77" s="9" t="inlineStr"/>
       <c r="C77" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -78752,11 +77380,7 @@
           <t>Mixed size</t>
         </is>
       </c>
-      <c r="B79" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B79" s="9" t="inlineStr"/>
       <c r="C79" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -78845,11 +77469,7 @@
           <t>Mixed grade</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B82" s="9" t="inlineStr"/>
       <c r="C82" s="9" t="inlineStr">
         <is>
           <t>14 (21.5%)</t>
@@ -78931,11 +77551,7 @@
           <t>Mixed grade</t>
         </is>
       </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 22</t>
-        </is>
-      </c>
+      <c r="B84" s="9" t="inlineStr"/>
       <c r="C84" s="9" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -79017,11 +77633,7 @@
           <t>Mixed grade</t>
         </is>
       </c>
-      <c r="B86" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 0</t>
-        </is>
-      </c>
+      <c r="B86" s="9" t="inlineStr"/>
       <c r="C86" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -79103,11 +77715,7 @@
           <t>Mixed grade</t>
         </is>
       </c>
-      <c r="B88" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 4</t>
-        </is>
-      </c>
+      <c r="B88" s="11" t="inlineStr"/>
       <c r="C88" s="11" t="inlineStr">
         <is>
           <t>0 (0.0%)</t>
@@ -79261,11 +77869,7 @@
           <t>Mixed size</t>
         </is>
       </c>
-      <c r="B97" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B97" s="9" t="inlineStr"/>
       <c r="C97" s="9" t="inlineStr">
         <is>
           <t>9 (13.8%)</t>
@@ -79347,11 +77951,7 @@
           <t>Mixed size</t>
         </is>
       </c>
-      <c r="B99" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 0</t>
-        </is>
-      </c>
+      <c r="B99" s="9" t="inlineStr"/>
       <c r="C99" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -79433,11 +78033,7 @@
           <t>Mixed size</t>
         </is>
       </c>
-      <c r="B101" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 0</t>
-        </is>
-      </c>
+      <c r="B101" s="9" t="inlineStr"/>
       <c r="C101" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -79519,11 +78115,7 @@
           <t>Mixed size</t>
         </is>
       </c>
-      <c r="B103" s="9" t="inlineStr">
-        <is>
-          <t>Exporter N = 0</t>
-        </is>
-      </c>
+      <c r="B103" s="9" t="inlineStr"/>
       <c r="C103" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -79612,11 +78204,7 @@
           <t>Mixed grade</t>
         </is>
       </c>
-      <c r="B106" s="9" t="inlineStr">
-        <is>
-          <t>Fisher N = 65</t>
-        </is>
-      </c>
+      <c r="B106" s="9" t="inlineStr"/>
       <c r="C106" s="9" t="inlineStr">
         <is>
           <t>6 (9.2%)</t>
@@ -79698,11 +78286,7 @@
           <t>Mixed grade</t>
         </is>
       </c>
-      <c r="B108" s="9" t="inlineStr">
-        <is>
-          <t>Middleman N = 0</t>
-        </is>
-      </c>
+      <c r="B108" s="9" t="inlineStr"/>
       <c r="C108" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -79784,11 +78368,7 @@
           <t>Mixed grade</t>
         </is>
       </c>
-      <c r="B110" s="9" t="inlineStr">
-        <is>
-          <t>Hotelier N = 0</t>
-        </is>
-      </c>
+      <c r="B110" s="9" t="inlineStr"/>
       <c r="C110" s="9" t="inlineStr">
         <is>
           <t>-</t>
@@ -79870,11 +78450,7 @@
           <t>Mixed grade</t>
         </is>
       </c>
-      <c r="B112" s="11" t="inlineStr">
-        <is>
-          <t>Exporter N = 0</t>
-        </is>
-      </c>
+      <c r="B112" s="11" t="inlineStr"/>
       <c r="C112" s="11" t="inlineStr">
         <is>
           <t>-</t>
